--- a/tables/N-Retention/Local_estpar_protection_True_vo_False_CUE_True.xlsx
+++ b/tables/N-Retention/Local_estpar_protection_True_vo_False_CUE_True.xlsx
@@ -573,61 +573,61 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2301739080636254</v>
+        <v>0.1675305560867122</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2038581421281848</v>
+        <v>0.2048268804697638</v>
       </c>
       <c r="M2" t="n">
-        <v>4.404174211659919</v>
+        <v>4.38984251428735</v>
       </c>
       <c r="N2" t="n">
-        <v>4.431700399547209</v>
+        <v>4.431577509285628</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002691171504999458</v>
+        <v>0.003854049432605141</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002705330698454973</v>
+        <v>0.002513810144188647</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007388549152359728</v>
+        <v>0.0007259513297994266</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000997255434131735</v>
+        <v>0.0009436081890589395</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0006271727938581915</v>
+        <v>0.0005963036596159674</v>
       </c>
       <c r="T2" t="n">
-        <v>0.008429017864844603</v>
+        <v>0.01448181018777471</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006114642423326417</v>
+        <v>0.007018797939499726</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001650794843199881</v>
+        <v>0.001587872777587131</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001951147332885655</v>
+        <v>0.001933331481129761</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001511763753361891</v>
+        <v>0.001469181096164335</v>
       </c>
     </row>
     <row r="3">
@@ -653,61 +653,61 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.124492385839805</v>
+        <v>0.07316695088643521</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5532083464448969</v>
+        <v>0.5545175457385235</v>
       </c>
       <c r="M3" t="n">
-        <v>4.381960123977297</v>
+        <v>4.382030300423189</v>
       </c>
       <c r="N3" t="n">
-        <v>4.404071920691782</v>
+        <v>4.415731695590146</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001259612093789209</v>
+        <v>0.001434853674305406</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001530035777980994</v>
+        <v>1e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4999999985043229</v>
+        <v>0.4999999999537261</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001550431826588159</v>
+        <v>0.001486040746615668</v>
       </c>
       <c r="S3" t="n">
-        <v>0.000975329272567693</v>
+        <v>0.0009307852208150012</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003100334623036593</v>
+        <v>0.01003026934999746</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002307662919526806</v>
+        <v>0.05003152840099899</v>
       </c>
       <c r="V3" t="n">
-        <v>818.6004660526391</v>
+        <v>1026.009405972069</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002384371718409499</v>
+        <v>0.002805823163154567</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001903218168187172</v>
+        <v>0.002405914353720911</v>
       </c>
     </row>
     <row r="4">
@@ -733,61 +733,61 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4194869142069372</v>
+        <v>0.3810454070602846</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2269941261492746</v>
+        <v>0.3185080960281653</v>
       </c>
       <c r="M4" t="n">
-        <v>4.305760231268049</v>
+        <v>4.287181927873305</v>
       </c>
       <c r="N4" t="n">
-        <v>4.56668237384806</v>
+        <v>4.55778091797234</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002736537092251788</v>
+        <v>0.003382546514949447</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002303346366714674</v>
+        <v>0.002195759944970705</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0003126656649177398</v>
+        <v>0.0003234696824555766</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001177591959986419</v>
+        <v>0.001190433937991362</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002881591816673855</v>
+        <v>0.0003758333140145145</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008055873523055262</v>
+        <v>0.0114694293836981</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006067695004082168</v>
+        <v>0.006295778694588904</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001290346321857133</v>
+        <v>0.001304103500119309</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002155231811894745</v>
+        <v>0.00226917224142402</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001631651105062255</v>
+        <v>0.001834764058601353</v>
       </c>
     </row>
     <row r="5">
@@ -813,61 +813,61 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1836362461632683</v>
+        <v>0.1248471362609869</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2222504215175351</v>
+        <v>0.2038780918013576</v>
       </c>
       <c r="M5" t="n">
-        <v>4.304261075601077</v>
+        <v>4.305018894746432</v>
       </c>
       <c r="N5" t="n">
-        <v>4.346505193495444</v>
+        <v>4.340541243551457</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002405051097681399</v>
+        <v>0.003463628587057707</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002171414992293701</v>
+        <v>0.002035862562924486</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0008481913763622973</v>
+        <v>0.0008345848484702018</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0008319833254017079</v>
+        <v>0.0007851159454450217</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001154947116980509</v>
+        <v>0.00109096203775671</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007421333634981275</v>
+        <v>0.01293629854800912</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004364052702698726</v>
+        <v>0.004969910522655495</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001913630896685506</v>
+        <v>0.001836553076979777</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001657996314740419</v>
+        <v>0.001620511725263467</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00246200615048302</v>
+        <v>0.002339777883210083</v>
       </c>
     </row>
     <row r="6">
@@ -893,61 +893,61 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1696932217433799</v>
+        <v>0.1116049959268887</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2020769593156199</v>
+        <v>0.168271775681717</v>
       </c>
       <c r="M6" t="n">
-        <v>4.366356260172854</v>
+        <v>4.368984812169352</v>
       </c>
       <c r="N6" t="n">
-        <v>4.383001713291498</v>
+        <v>4.375968469678424</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001864778329239148</v>
+        <v>0.002641914328019859</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001386264623010574</v>
+        <v>0.001192275056696484</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0005315633612411854</v>
+        <v>0.0005234876477734115</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003945333144469372</v>
+        <v>0.0003572762133770825</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003435923367472196</v>
+        <v>0.0002987848966193263</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005574953053647987</v>
+        <v>0.009342482430974372</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002577185594421582</v>
+        <v>0.002648112185490498</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001211483231857958</v>
+        <v>0.001173605405648692</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009675876449548447</v>
+        <v>0.0009355964729787013</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001032152398687266</v>
+        <v>0.0009712145956040581</v>
       </c>
     </row>
     <row r="7">
@@ -973,61 +973,61 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2323659267012791</v>
+        <v>0.1710238365812231</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1608106854598932</v>
+        <v>0.1653321556771652</v>
       </c>
       <c r="M7" t="n">
-        <v>4.276212554625182</v>
+        <v>4.248631377567689</v>
       </c>
       <c r="N7" t="n">
-        <v>4.381946798166521</v>
+        <v>4.383415149377444</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003149298535983989</v>
+        <v>0.00477183121353866</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001922034526403117</v>
+        <v>0.001788911632350727</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0005476915701763671</v>
+        <v>0.0005397995102645563</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009223081521792648</v>
+        <v>0.0008690850460929253</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004824989991914129</v>
+        <v>0.0004637881951211703</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01061515508883203</v>
+        <v>0.01938964740920257</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004548978106683909</v>
+        <v>0.005283407588549342</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001257180777970648</v>
+        <v>0.001228147669275887</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001739891691583329</v>
+        <v>0.001716266030686674</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001817617360222505</v>
+        <v>0.001840293588075687</v>
       </c>
     </row>
     <row r="8">
@@ -1053,61 +1053,61 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1752392312349113</v>
+        <v>0.1151420474620844</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1425137369877896</v>
+        <v>0.1534965944746647</v>
       </c>
       <c r="M8" t="n">
-        <v>4.438028116501265</v>
+        <v>4.414719551879695</v>
       </c>
       <c r="N8" t="n">
-        <v>4.410528672138936</v>
+        <v>4.415178591099621</v>
       </c>
       <c r="O8" t="n">
-        <v>0.005256587018313837</v>
+        <v>0.008739230429296835</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002931314599215531</v>
+        <v>0.003286112089232933</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009976106446216845</v>
+        <v>0.0009894532877880772</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001447216483273919</v>
+        <v>0.001395893530182093</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0006762304146011792</v>
+        <v>0.0006528528641778301</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02118161033348079</v>
+        <v>0.04463855216582915</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01028679731082227</v>
+        <v>0.01610174471284386</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002310414630882934</v>
+        <v>0.002239156479592848</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003124986607597718</v>
+        <v>0.003103386188076283</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001421505330282355</v>
+        <v>0.00137417615889978</v>
       </c>
     </row>
     <row r="9">
@@ -1133,61 +1133,61 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2156188681478334</v>
+        <v>0.1553258947904939</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1618976166042267</v>
+        <v>0.1659236344307104</v>
       </c>
       <c r="M9" t="n">
-        <v>4.239179655326522</v>
+        <v>4.219349096074717</v>
       </c>
       <c r="N9" t="n">
-        <v>4.367297389065749</v>
+        <v>4.366191000577103</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004296510364102662</v>
+        <v>0.006645392829855584</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002637978233546663</v>
+        <v>0.002639840552013611</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.000748392200056645</v>
+        <v>0.0007395245078955063</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0009155455521792674</v>
+        <v>0.0008768692005606429</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0008146157920046849</v>
+        <v>0.0007893677636070934</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01518459200985857</v>
+        <v>0.0288798581052783</v>
       </c>
       <c r="U9" t="n">
-        <v>0.006909445556981124</v>
+        <v>0.00941563516710562</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001676023976063113</v>
+        <v>0.001626582675018997</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001757081587215729</v>
+        <v>0.001769065799162649</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001634896073593201</v>
+        <v>0.001608982662520165</v>
       </c>
     </row>
     <row r="10">
@@ -1213,61 +1213,61 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2191421967246366</v>
+        <v>0.160196857539937</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1210502082218665</v>
+        <v>0.1309199116146302</v>
       </c>
       <c r="M10" t="n">
-        <v>4.127028746765415</v>
+        <v>4.102673349198579</v>
       </c>
       <c r="N10" t="n">
-        <v>4.237976715739199</v>
+        <v>4.239142941185931</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0043127406853667</v>
+        <v>0.00730466872130718</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002997040904358447</v>
+        <v>0.003699432372662467</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0005597470493065694</v>
+        <v>0.0005537132764520121</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001036492123135173</v>
+        <v>0.0009741794873899478</v>
       </c>
       <c r="S10" t="n">
-        <v>0.000589435009939186</v>
+        <v>0.0005762496550838307</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01700937137872132</v>
+        <v>0.037149574000781</v>
       </c>
       <c r="U10" t="n">
-        <v>0.009802894992340185</v>
+        <v>0.01777656620736351</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001281933332621773</v>
+        <v>0.001259869388137926</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001957326352422647</v>
+        <v>0.001936757114400767</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001308575240115257</v>
+        <v>0.00132019908497627</v>
       </c>
     </row>
     <row r="11">
@@ -1293,61 +1293,61 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4197102286204545</v>
+        <v>0.3872233474870604</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4029634621908609</v>
+        <v>0.4276425842664839</v>
       </c>
       <c r="M11" t="n">
-        <v>4.128911664621688</v>
+        <v>4.108821795020701</v>
       </c>
       <c r="N11" t="n">
-        <v>4.273335182572387</v>
+        <v>4.282370996086425</v>
       </c>
       <c r="O11" t="n">
-        <v>0.002217885434340052</v>
+        <v>0.002935934123242926</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002087746069179515</v>
+        <v>0.001930345081611625</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001438915254901196</v>
+        <v>0.00131883478838968</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002601759047055789</v>
+        <v>0.002555986268434837</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002099497949211785</v>
+        <v>0.002072073839027572</v>
       </c>
       <c r="T11" t="n">
-        <v>0.005739380590142033</v>
+        <v>0.00958384939536518</v>
       </c>
       <c r="U11" t="n">
-        <v>0.004083042785970337</v>
+        <v>0.003407093719423067</v>
       </c>
       <c r="V11" t="n">
-        <v>0.003383277043049416</v>
+        <v>0.003089191486455324</v>
       </c>
       <c r="W11" t="n">
-        <v>0.004046666836828186</v>
+        <v>0.004338049683661311</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003915948235742963</v>
+        <v>0.00392334501501865</v>
       </c>
     </row>
     <row r="12">
@@ -1373,61 +1373,61 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1394114541171846</v>
+        <v>0.0922222144048621</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1456736305632342</v>
+        <v>0.4574356711026707</v>
       </c>
       <c r="M12" t="n">
-        <v>4.056914465248047</v>
+        <v>4.245803122192966</v>
       </c>
       <c r="N12" t="n">
-        <v>4.115886547660843</v>
+        <v>4.260854608340761</v>
       </c>
       <c r="O12" t="n">
-        <v>0.00210670066747663</v>
+        <v>0.0008106635282717026</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001609352165611628</v>
+        <v>0.003310818887474191</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0005356394104224404</v>
+        <v>0.002453027373664869</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001361294186320092</v>
+        <v>0.006579355747714607</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0005300169056709032</v>
+        <v>0.001227750045827068</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0089042028405249</v>
+        <v>0.002138181762319013</v>
       </c>
       <c r="U12" t="n">
-        <v>0.007867804813946068</v>
+        <v>0.004002539604045456</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001217794661640005</v>
+        <v>0.004908039837014861</v>
       </c>
       <c r="W12" t="n">
-        <v>0.006934540255497371</v>
+        <v>0.01001310545712505</v>
       </c>
       <c r="X12" t="n">
-        <v>0.001151757207677912</v>
+        <v>0.0018117219538873</v>
       </c>
     </row>
     <row r="13">
@@ -1453,61 +1453,61 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3157071197613084</v>
+        <v>0.2602259461942728</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2737076648369285</v>
+        <v>0.2420118569889327</v>
       </c>
       <c r="M13" t="n">
-        <v>4.293313089366361</v>
+        <v>4.287383668443933</v>
       </c>
       <c r="N13" t="n">
-        <v>4.508972440145752</v>
+        <v>4.513211862890015</v>
       </c>
       <c r="O13" t="n">
-        <v>0.002700967855301697</v>
+        <v>0.003092716977852132</v>
       </c>
       <c r="P13" t="n">
-        <v>0.002176422003469177</v>
+        <v>0.002111715658147931</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001066482777578717</v>
+        <v>0.0009926616053976486</v>
       </c>
       <c r="R13" t="n">
-        <v>0.009237283221451868</v>
+        <v>0.008930002710080532</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01538813171462382</v>
+        <v>0.0150593969535081</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01482684965159497</v>
+        <v>0.01787879337612956</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03391529403917854</v>
+        <v>0.03170473801136639</v>
       </c>
       <c r="V13" t="n">
-        <v>0.006321883732496094</v>
+        <v>0.006233389501745975</v>
       </c>
       <c r="W13" t="n">
-        <v>0.01764366998249719</v>
+        <v>0.01744718747863987</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03717166058851476</v>
+        <v>0.03647404045558665</v>
       </c>
     </row>
     <row r="14">
@@ -1533,61 +1533,61 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2052549529133269</v>
+        <v>0.1437589046858702</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2823423531130162</v>
+        <v>0.2263241572974352</v>
       </c>
       <c r="M14" t="n">
-        <v>4.397072460739371</v>
+        <v>4.390242826472774</v>
       </c>
       <c r="N14" t="n">
-        <v>4.362462705763203</v>
+        <v>4.350277337599792</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01400422881849595</v>
+        <v>0.01788998214124655</v>
       </c>
       <c r="P14" t="n">
-        <v>1.000000000068941e-05</v>
+        <v>0.0009659493158368145</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.007796899182247439</v>
+        <v>0.007165596222226686</v>
       </c>
       <c r="R14" t="n">
-        <v>0.007193774105648064</v>
+        <v>0.006154539299376085</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01081755134281249</v>
+        <v>0.008828397700010654</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1770222781884504</v>
+        <v>0.05455122685825393</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6360448956295541</v>
+        <v>0.07484154703190608</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01637687903346208</v>
+        <v>0.01510222819423206</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01554952738717896</v>
+        <v>0.0137729437606315</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03148061678100911</v>
+        <v>0.02666130562051727</v>
       </c>
     </row>
     <row r="15">
@@ -1613,61 +1613,61 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1874830231703039</v>
+        <v>0.1307591005177591</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2738406689335328</v>
+        <v>0.2273896064186872</v>
       </c>
       <c r="M15" t="n">
-        <v>4.085204214067701</v>
+        <v>4.079261036110907</v>
       </c>
       <c r="N15" t="n">
-        <v>4.242020397769503</v>
+        <v>4.223894393655108</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01254241917934499</v>
+        <v>0.01631021968681497</v>
       </c>
       <c r="P15" t="n">
-        <v>0.004808876702551187</v>
+        <v>0.004127096205365092</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.007628422515599419</v>
+        <v>0.007373053898522652</v>
       </c>
       <c r="R15" t="n">
-        <v>0.005527788073275897</v>
+        <v>0.00472099740469856</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02496862696886337</v>
+        <v>0.02287937334887536</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03198667718042063</v>
+        <v>0.04872768288020187</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01483979876365708</v>
+        <v>0.01637470834662126</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01635488726136984</v>
+        <v>0.01579128497194075</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01216612177749948</v>
+        <v>0.01142315549228086</v>
       </c>
       <c r="X15" t="n">
-        <v>0.08699806654188172</v>
+        <v>0.07802305702130345</v>
       </c>
     </row>
     <row r="16">
@@ -1693,61 +1693,61 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5161649251798621</v>
+        <v>0.5129655543643412</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5289027221649324</v>
+        <v>0.557259640164412</v>
       </c>
       <c r="M16" t="n">
-        <v>4.346437810309332</v>
+        <v>4.407580888704488</v>
       </c>
       <c r="N16" t="n">
-        <v>4.497654451769204</v>
+        <v>4.533891488100918</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0281651377694198</v>
+        <v>0.0281033980222152</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01958518096781141</v>
+        <v>0.01962191051292817</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01984915215896495</v>
+        <v>0.02089202593957276</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01270990256982217</v>
+        <v>0.01324684577104615</v>
       </c>
       <c r="S16" t="n">
-        <v>0.02222029913265714</v>
+        <v>0.006392029570576234</v>
       </c>
       <c r="T16" t="n">
-        <v>0.08447027587891738</v>
+        <v>0.4081434550788374</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03338788909631528</v>
+        <v>0.3437940804518302</v>
       </c>
       <c r="V16" t="n">
-        <v>0.05598673841203895</v>
+        <v>0.3070877940680208</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03195524007674559</v>
+        <v>0.1782552037006788</v>
       </c>
       <c r="X16" t="n">
-        <v>18.89505989157118</v>
+        <v>40.00688704927386</v>
       </c>
     </row>
     <row r="17">
@@ -1773,61 +1773,61 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2110178984664703</v>
+        <v>0.1557936046085961</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2661580531266374</v>
+        <v>0.2186598458224473</v>
       </c>
       <c r="M17" t="n">
-        <v>3.870271546959827</v>
+        <v>3.843478583732289</v>
       </c>
       <c r="N17" t="n">
-        <v>4.03490937508337</v>
+        <v>4.003957091057472</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01288404957265711</v>
+        <v>0.01648834078966527</v>
       </c>
       <c r="P17" t="n">
-        <v>0.003307742984945284</v>
+        <v>0.002203229778118012</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.006651693446382009</v>
+        <v>0.006498393042520786</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004635637104796302</v>
+        <v>0.003791007255171619</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01071433425586029</v>
+        <v>0.01035876462970347</v>
       </c>
       <c r="T17" t="n">
-        <v>0.03198970135452727</v>
+        <v>0.04703005936744935</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01751074369670334</v>
+        <v>0.01607643618150006</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01394410733891334</v>
+        <v>0.01364663172357149</v>
       </c>
       <c r="W17" t="n">
-        <v>0.01058951568384074</v>
+        <v>0.009870199832760407</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02090999480590296</v>
+        <v>0.02040256571215567</v>
       </c>
     </row>
     <row r="18">
@@ -1853,61 +1853,61 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2424607087442707</v>
+        <v>0.1816593812827441</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2651971061528096</v>
+        <v>0.2297599240156478</v>
       </c>
       <c r="M18" t="n">
-        <v>4.298420190621356</v>
+        <v>4.289171463703494</v>
       </c>
       <c r="N18" t="n">
-        <v>4.300116150274684</v>
+        <v>4.29001168622623</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01326870139802743</v>
+        <v>0.01739261734314398</v>
       </c>
       <c r="P18" t="n">
-        <v>0.006809503203409333</v>
+        <v>0.006830928706074936</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.006045214067951051</v>
+        <v>0.005864640039434408</v>
       </c>
       <c r="R18" t="n">
-        <v>0.008471813273374094</v>
+        <v>0.007731479483988783</v>
       </c>
       <c r="S18" t="n">
-        <v>0.008835381506191332</v>
+        <v>0.008269234149345694</v>
       </c>
       <c r="T18" t="n">
-        <v>0.03311493142453596</v>
+        <v>0.05021187966092077</v>
       </c>
       <c r="U18" t="n">
-        <v>0.01546026927990645</v>
+        <v>0.01787639024362694</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01276674356694847</v>
+        <v>0.01241972120058862</v>
       </c>
       <c r="W18" t="n">
-        <v>0.01479202865830817</v>
+        <v>0.01426045826164472</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01543526946701237</v>
+        <v>0.01483387158463595</v>
       </c>
     </row>
     <row r="19">
@@ -1933,61 +1933,61 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.161033465819801</v>
+        <v>0.107691775349662</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2233885571873788</v>
+        <v>0.1758416743262448</v>
       </c>
       <c r="M19" t="n">
-        <v>3.990866149206148</v>
+        <v>3.99750997059567</v>
       </c>
       <c r="N19" t="n">
-        <v>4.377813604369669</v>
+        <v>4.368548141329543</v>
       </c>
       <c r="O19" t="n">
-        <v>0.004944859657935866</v>
+        <v>0.006398901137877754</v>
       </c>
       <c r="P19" t="n">
-        <v>0.009647790526085663</v>
+        <v>0.009313786462988539</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.003380252631110283</v>
+        <v>0.003312838791621745</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001508451365663482</v>
+        <v>0.001365805554459212</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03165977277557139</v>
+        <v>0.02905336378899924</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01933349438468121</v>
+        <v>0.02716891950590889</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02425993118002748</v>
+        <v>0.02601667078406661</v>
       </c>
       <c r="V19" t="n">
-        <v>0.008963682648373789</v>
+        <v>0.008823830071816474</v>
       </c>
       <c r="W19" t="n">
-        <v>0.006852669240307164</v>
+        <v>0.006621070205702204</v>
       </c>
       <c r="X19" t="n">
-        <v>0.159790445284404</v>
+        <v>0.1377689274951135</v>
       </c>
     </row>
     <row r="20">
@@ -2013,61 +2013,61 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2706740016525256</v>
+        <v>0.2057022057339838</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2927341412025184</v>
+        <v>0.2460353464898241</v>
       </c>
       <c r="M20" t="n">
-        <v>4.627752525577289</v>
+        <v>4.630732926731516</v>
       </c>
       <c r="N20" t="n">
-        <v>4.593214902107496</v>
+        <v>4.596083151047137</v>
       </c>
       <c r="O20" t="n">
-        <v>0.008405074024867456</v>
+        <v>0.0103417849159518</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0008181292013049757</v>
+        <v>1.000000000000963e-05</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.004350963669534897</v>
+        <v>0.004347903284454896</v>
       </c>
       <c r="R20" t="n">
-        <v>0.005514120826268748</v>
+        <v>0.005119101740639123</v>
       </c>
       <c r="S20" t="n">
-        <v>0.01512166055457031</v>
+        <v>0.01285926643958463</v>
       </c>
       <c r="T20" t="n">
-        <v>0.02149601195623009</v>
+        <v>0.02918269803251593</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01607547089742069</v>
+        <v>0.01705318662732906</v>
       </c>
       <c r="V20" t="n">
-        <v>0.01013008342966108</v>
+        <v>0.0100686371778519</v>
       </c>
       <c r="W20" t="n">
-        <v>0.01141365875624619</v>
+        <v>0.01102993125728473</v>
       </c>
       <c r="X20" t="n">
-        <v>0.02918885627428229</v>
+        <v>0.02694208264364232</v>
       </c>
     </row>
     <row r="21">
@@ -2093,61 +2093,61 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1202941340488625</v>
+        <v>0.07261609984294198</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1378533115986938</v>
+        <v>0.1314178125355716</v>
       </c>
       <c r="M21" t="n">
-        <v>4.107682434211664</v>
+        <v>4.163497628306884</v>
       </c>
       <c r="N21" t="n">
-        <v>4.121165225382007</v>
+        <v>4.130754803237112</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01552863482697239</v>
+        <v>0.0189004924063926</v>
       </c>
       <c r="P21" t="n">
-        <v>0.05125495867531689</v>
+        <v>0.06249404395426711</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.00495496347823411</v>
+        <v>0.006481828016717642</v>
       </c>
       <c r="R21" t="n">
-        <v>1.000000000033484e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>1.000000000931178e-05</v>
+        <v>1.000000000001769e-05</v>
       </c>
       <c r="T21" t="n">
-        <v>0.05404724424884073</v>
+        <v>0.08128145033746066</v>
       </c>
       <c r="U21" t="n">
-        <v>0.159252307059572</v>
+        <v>0.2450136175425877</v>
       </c>
       <c r="V21" t="n">
-        <v>0.01426035089263716</v>
+        <v>0.01982066511612264</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01114106901589464</v>
+        <v>0.01276218550501924</v>
       </c>
       <c r="X21" t="n">
-        <v>0.03839815370889071</v>
+        <v>0.05859776011175964</v>
       </c>
     </row>
     <row r="22">
@@ -2173,61 +2173,61 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3065794238146419</v>
+        <v>0.2535748896970106</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3244300250308248</v>
+        <v>0.2788887968123748</v>
       </c>
       <c r="M22" t="n">
-        <v>4.136683456812678</v>
+        <v>4.130086663000352</v>
       </c>
       <c r="N22" t="n">
-        <v>4.309737666697521</v>
+        <v>4.298500606978414</v>
       </c>
       <c r="O22" t="n">
-        <v>0.005782422350832007</v>
+        <v>0.006872253663045675</v>
       </c>
       <c r="P22" t="n">
-        <v>4.263622307777646e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.002652481887162014</v>
+        <v>0.002633998113527869</v>
       </c>
       <c r="R22" t="n">
-        <v>0.003432749035792017</v>
+        <v>0.003212239643198801</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01265005310603557</v>
+        <v>0.01205624202677407</v>
       </c>
       <c r="T22" t="n">
-        <v>0.01622574082685344</v>
+        <v>0.02008115770515083</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0131990550313002</v>
+        <v>0.01278400450270836</v>
       </c>
       <c r="V22" t="n">
-        <v>0.008401332216469187</v>
+        <v>0.008374303456408348</v>
       </c>
       <c r="W22" t="n">
-        <v>0.009118648353735702</v>
+        <v>0.008780055244100096</v>
       </c>
       <c r="X22" t="n">
-        <v>0.02728647340827925</v>
+        <v>0.02617285586858337</v>
       </c>
     </row>
     <row r="23">
@@ -2253,61 +2253,61 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2861768349137373</v>
+        <v>0.2372061265604153</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2868587543547503</v>
+        <v>0.2519977610719498</v>
       </c>
       <c r="M23" t="n">
-        <v>3.86931123372123</v>
+        <v>3.867552161569812</v>
       </c>
       <c r="N23" t="n">
-        <v>4.121094712711209</v>
+        <v>4.101239360364485</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01080203276763439</v>
+        <v>0.01375377271582779</v>
       </c>
       <c r="P23" t="n">
-        <v>0.004323766369731778</v>
+        <v>0.003866975210643686</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.004035792530641495</v>
+        <v>0.003868720726163511</v>
       </c>
       <c r="R23" t="n">
-        <v>0.006691106345688863</v>
+        <v>0.005574761657859744</v>
       </c>
       <c r="S23" t="n">
-        <v>0.02494506376382187</v>
+        <v>0.02338365265835273</v>
       </c>
       <c r="T23" t="n">
-        <v>0.02712443125045513</v>
+        <v>0.03920583727387889</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0189504119050401</v>
+        <v>0.0179985275041024</v>
       </c>
       <c r="V23" t="n">
-        <v>0.009651168672436948</v>
+        <v>0.009425583962642438</v>
       </c>
       <c r="W23" t="n">
-        <v>0.0121481504010053</v>
+        <v>0.01162460550030269</v>
       </c>
       <c r="X23" t="n">
-        <v>0.07733279821195653</v>
+        <v>0.07109329961311782</v>
       </c>
     </row>
     <row r="24">
@@ -2333,61 +2333,61 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3875416039382416</v>
+        <v>0.3446324318476313</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4585213846789534</v>
+        <v>0.452020538268895</v>
       </c>
       <c r="M24" t="n">
-        <v>4.305819674281706</v>
+        <v>4.315611646840071</v>
       </c>
       <c r="N24" t="n">
-        <v>4.373982753815935</v>
+        <v>4.364672008334238</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01335184653723498</v>
+        <v>0.01418672412253162</v>
       </c>
       <c r="P24" t="n">
-        <v>0.009495457683851587</v>
+        <v>0.009568504000572138</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.01324016456593231</v>
+        <v>0.0131546271725437</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01331352524374036</v>
+        <v>0.01303765519961699</v>
       </c>
       <c r="S24" t="n">
-        <v>1.000000002711727e-05</v>
+        <v>1.000000000000016e-05</v>
       </c>
       <c r="T24" t="n">
-        <v>0.04057200417275288</v>
+        <v>0.0671877340657514</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0266029510037471</v>
+        <v>0.0393448202960815</v>
       </c>
       <c r="V24" t="n">
-        <v>0.03168082067550165</v>
+        <v>0.03162314203714289</v>
       </c>
       <c r="W24" t="n">
-        <v>0.02984261827472873</v>
+        <v>0.02311918699882783</v>
       </c>
       <c r="X24" t="n">
-        <v>2.832379455353822</v>
+        <v>3.591836590380365</v>
       </c>
     </row>
     <row r="25">
@@ -2413,61 +2413,61 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.215848059616466</v>
+        <v>0.1556201893189063</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2284594467336942</v>
+        <v>0.1790189136154802</v>
       </c>
       <c r="M25" t="n">
-        <v>4.310157944037903</v>
+        <v>4.317303423812332</v>
       </c>
       <c r="N25" t="n">
-        <v>4.340621142564224</v>
+        <v>4.341380298872839</v>
       </c>
       <c r="O25" t="n">
-        <v>0.002231536890875667</v>
+        <v>0.00300498158514161</v>
       </c>
       <c r="P25" t="n">
-        <v>1.00000000000183e-05</v>
+        <v>1.000000000000013e-05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0005427421474549116</v>
+        <v>0.0005914794219626882</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0003337243919490771</v>
+        <v>0.0003192861493801596</v>
       </c>
       <c r="S25" t="n">
-        <v>9.811530508613571e-05</v>
+        <v>7.319086832606948e-05</v>
       </c>
       <c r="T25" t="n">
-        <v>0.005387245478812809</v>
+        <v>0.007940678178872469</v>
       </c>
       <c r="U25" t="n">
-        <v>0.002879068444643339</v>
+        <v>0.003267684661634188</v>
       </c>
       <c r="V25" t="n">
-        <v>0.001544802675924805</v>
+        <v>0.001600596823571486</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001344254172780884</v>
+        <v>0.00131732034540001</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001314073681162972</v>
+        <v>0.001298920647312621</v>
       </c>
     </row>
     <row r="26">
@@ -2493,61 +2493,61 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3197948172394026</v>
+        <v>0.2658710797035032</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3076761724502429</v>
+        <v>0.267236756879264</v>
       </c>
       <c r="M26" t="n">
-        <v>4.224153844393832</v>
+        <v>4.209752341131509</v>
       </c>
       <c r="N26" t="n">
-        <v>4.299738132353408</v>
+        <v>4.288592832345312</v>
       </c>
       <c r="O26" t="n">
-        <v>0.002886451885566999</v>
+        <v>0.003501881328880443</v>
       </c>
       <c r="P26" t="n">
-        <v>0.001543354958377238</v>
+        <v>0.001333305726534032</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.000660358953136808</v>
+        <v>0.0006280711980899499</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0005625695089046828</v>
+        <v>0.0004991557484121078</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003215504714468515</v>
+        <v>0.0002789492508540321</v>
       </c>
       <c r="T26" t="n">
-        <v>0.005709499860443091</v>
+        <v>0.007543815995314331</v>
       </c>
       <c r="U26" t="n">
-        <v>0.002436937228166082</v>
+        <v>0.002329226323486624</v>
       </c>
       <c r="V26" t="n">
-        <v>0.00171961532673345</v>
+        <v>0.001682785369071658</v>
       </c>
       <c r="W26" t="n">
-        <v>0.001513624191671615</v>
+        <v>0.001465860506004005</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001258532393978183</v>
+        <v>0.001238211879703194</v>
       </c>
     </row>
     <row r="27">
@@ -2573,61 +2573,61 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2439507965539418</v>
+        <v>0.1853792209497878</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3067422390276155</v>
+        <v>0.2584091786475279</v>
       </c>
       <c r="M27" t="n">
-        <v>4.149671453558346</v>
+        <v>4.135160058706046</v>
       </c>
       <c r="N27" t="n">
-        <v>4.151068964910465</v>
+        <v>4.129305238841737</v>
       </c>
       <c r="O27" t="n">
-        <v>0.001458714140586512</v>
+        <v>0.001731396150195134</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0005687835756680706</v>
+        <v>0.0003003211034702188</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.00119843705062235</v>
+        <v>0.001184104518192363</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0006419722126537749</v>
+        <v>0.000537613651776248</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0007223262149807405</v>
+        <v>0.0006850676245755442</v>
       </c>
       <c r="T27" t="n">
-        <v>0.003386164804875829</v>
+        <v>0.004392134417186663</v>
       </c>
       <c r="U27" t="n">
-        <v>0.00242254127015918</v>
+        <v>0.002434931435213605</v>
       </c>
       <c r="V27" t="n">
-        <v>0.002472152956502945</v>
+        <v>0.002460741437311616</v>
       </c>
       <c r="W27" t="n">
-        <v>0.001712390984599777</v>
+        <v>0.001625009656909543</v>
       </c>
       <c r="X27" t="n">
-        <v>0.001794196421560956</v>
+        <v>0.001768732302565485</v>
       </c>
     </row>
     <row r="28">
@@ -2653,61 +2653,61 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3989355859737008</v>
+        <v>0.3642355007425858</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4106032945272304</v>
+        <v>0.4013540404293284</v>
       </c>
       <c r="M28" t="n">
-        <v>4.114744150286834</v>
+        <v>4.119195011468114</v>
       </c>
       <c r="N28" t="n">
-        <v>4.294212825374541</v>
+        <v>4.289586132641451</v>
       </c>
       <c r="O28" t="n">
-        <v>0.002003778012629163</v>
+        <v>0.002214651293898889</v>
       </c>
       <c r="P28" t="n">
-        <v>1.000000000000001e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.001514721204578129</v>
+        <v>0.001543133780512999</v>
       </c>
       <c r="R28" t="n">
-        <v>0.005014509921176631</v>
+        <v>0.0049955060723392</v>
       </c>
       <c r="S28" t="n">
-        <v>0.01036748911970494</v>
+        <v>0.01018175815249011</v>
       </c>
       <c r="T28" t="n">
-        <v>0.004603882127273048</v>
+        <v>0.005358066477322003</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0109147464033905</v>
+        <v>0.01045295138156045</v>
       </c>
       <c r="V28" t="n">
-        <v>0.003314082380949613</v>
+        <v>0.003416733247732091</v>
       </c>
       <c r="W28" t="n">
-        <v>0.009606168154501459</v>
+        <v>0.01048609179579119</v>
       </c>
       <c r="X28" t="n">
-        <v>0.02351987533586998</v>
+        <v>0.02336936242519417</v>
       </c>
     </row>
     <row r="29">
@@ -2733,61 +2733,61 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5337507387871602</v>
+        <v>0.541363956397434</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3455125462067315</v>
+        <v>0.523576445841029</v>
       </c>
       <c r="M29" t="n">
-        <v>4.255427909449321</v>
+        <v>4.316787024057529</v>
       </c>
       <c r="N29" t="n">
-        <v>4.202276187780864</v>
+        <v>4.269220077614253</v>
       </c>
       <c r="O29" t="n">
-        <v>0.004750996569864848</v>
+        <v>0.004070993851702244</v>
       </c>
       <c r="P29" t="n">
-        <v>0.01809454868918335</v>
+        <v>0.01910672843730625</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0001807004228334998</v>
+        <v>0.0008484369058424253</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01725164143317796</v>
+        <v>0.02113150125770955</v>
       </c>
       <c r="S29" t="n">
-        <v>0.009480158620399576</v>
+        <v>0.01040541863446287</v>
       </c>
       <c r="T29" t="n">
-        <v>0.009135815873177288</v>
+        <v>0.006805880669072288</v>
       </c>
       <c r="U29" t="n">
-        <v>0.06252823516812714</v>
+        <v>0.07573825798056674</v>
       </c>
       <c r="V29" t="n">
-        <v>0.002987836248732887</v>
+        <v>0.003525289405341013</v>
       </c>
       <c r="W29" t="n">
-        <v>0.03301411606916037</v>
+        <v>0.04776847093810734</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01607130683896535</v>
+        <v>0.01792079846937225</v>
       </c>
     </row>
     <row r="30">
@@ -2813,61 +2813,61 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5332067105517685</v>
+        <v>0.5214438824954322</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4025904287746107</v>
+        <v>0.4584581903174956</v>
       </c>
       <c r="M30" t="n">
-        <v>4.521248121695771</v>
+        <v>4.530502495651595</v>
       </c>
       <c r="N30" t="n">
-        <v>4.311352218127467</v>
+        <v>4.320239225007002</v>
       </c>
       <c r="O30" t="n">
-        <v>0.002550230994724858</v>
+        <v>0.002698930483360697</v>
       </c>
       <c r="P30" t="n">
-        <v>0.004936681371493739</v>
+        <v>0.004786950071345539</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0002430560923556653</v>
+        <v>0.0003275455185707774</v>
       </c>
       <c r="R30" t="n">
-        <v>0.00954011088617919</v>
+        <v>0.01009428636547875</v>
       </c>
       <c r="S30" t="n">
-        <v>0.004191762445509326</v>
+        <v>0.004551572335120736</v>
       </c>
       <c r="T30" t="n">
-        <v>0.004976797964929932</v>
+        <v>0.005333015559697542</v>
       </c>
       <c r="U30" t="n">
-        <v>0.008966759538751432</v>
+        <v>0.008331146401263903</v>
       </c>
       <c r="V30" t="n">
-        <v>0.003026178362672638</v>
+        <v>0.00317666374283758</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01637644842134905</v>
+        <v>0.01824151334180046</v>
       </c>
       <c r="X30" t="n">
-        <v>0.005671886662416395</v>
+        <v>0.006266829795770968</v>
       </c>
     </row>
     <row r="31">
@@ -2893,61 +2893,61 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4902078464552742</v>
+        <v>0.4761534586665042</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4307282667397589</v>
+        <v>0.4435755784201663</v>
       </c>
       <c r="M31" t="n">
-        <v>4.249538389327932</v>
+        <v>4.256876131451557</v>
       </c>
       <c r="N31" t="n">
-        <v>4.410351733710971</v>
+        <v>4.406501501649976</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002730239733842983</v>
+        <v>0.002837765847474639</v>
       </c>
       <c r="P31" t="n">
-        <v>0.007275503169651897</v>
+        <v>0.006895209102495803</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0002667186749248477</v>
+        <v>0.0002659987817971182</v>
       </c>
       <c r="R31" t="n">
-        <v>0.001785835699265363</v>
+        <v>0.001796465695426211</v>
       </c>
       <c r="S31" t="n">
-        <v>0.00056394847497899</v>
+        <v>0.0005773366436962788</v>
       </c>
       <c r="T31" t="n">
-        <v>0.004947534112347361</v>
+        <v>0.005244506604222339</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01692632058017633</v>
+        <v>0.01498676172744096</v>
       </c>
       <c r="V31" t="n">
-        <v>0.00255117353923214</v>
+        <v>0.002600231076028347</v>
       </c>
       <c r="W31" t="n">
-        <v>0.003007772002258971</v>
+        <v>0.003174667230699651</v>
       </c>
       <c r="X31" t="n">
-        <v>0.002801064412960188</v>
+        <v>0.002898112892481788</v>
       </c>
     </row>
     <row r="32">
@@ -2973,61 +2973,61 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5003204670714311</v>
+        <v>0.4784259818721357</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4277098015031122</v>
+        <v>0.4395375417643161</v>
       </c>
       <c r="M32" t="n">
-        <v>4.53028971271256</v>
+        <v>4.54395154441503</v>
       </c>
       <c r="N32" t="n">
-        <v>4.426130147752106</v>
+        <v>4.423048245990696</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0008350083291765586</v>
+        <v>0.0009157733761689355</v>
       </c>
       <c r="P32" t="n">
-        <v>0.005247746006639017</v>
+        <v>0.00518126371884231</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.000000000000001e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.004418886554165519</v>
+        <v>0.004562738219853206</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001401838780852578</v>
+        <v>0.001424639663582253</v>
       </c>
       <c r="T32" t="n">
-        <v>0.00281365799203623</v>
+        <v>0.0030684238680674</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0113549929956145</v>
+        <v>0.01087878385678573</v>
       </c>
       <c r="V32" t="n">
-        <v>0.002600330117320171</v>
+        <v>0.002618432918736213</v>
       </c>
       <c r="W32" t="n">
-        <v>0.008108609775447266</v>
+        <v>0.008778150161159445</v>
       </c>
       <c r="X32" t="n">
-        <v>0.003592609364448746</v>
+        <v>0.003666927493215529</v>
       </c>
     </row>
     <row r="33">
@@ -3051,61 +3051,61 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2851358817564152</v>
+        <v>0.2262549868912993</v>
       </c>
       <c r="L33" t="n">
-        <v>0.318932250993743</v>
+        <v>0.2965494809834754</v>
       </c>
       <c r="M33" t="n">
-        <v>4.308512879316226</v>
+        <v>4.301098115789768</v>
       </c>
       <c r="N33" t="n">
-        <v>4.270877230228868</v>
+        <v>4.26286686107843</v>
       </c>
       <c r="O33" t="n">
-        <v>0.006255038232011506</v>
+        <v>0.007706245063438562</v>
       </c>
       <c r="P33" t="n">
-        <v>0.004238498551876357</v>
+        <v>0.002426124663233034</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003966480546542436</v>
+        <v>0.003904030670491616</v>
       </c>
       <c r="R33" t="n">
-        <v>0.007572420642581414</v>
+        <v>0.007029752232605614</v>
       </c>
       <c r="S33" t="n">
-        <v>0.004151247082158103</v>
+        <v>0.003845834602410518</v>
       </c>
       <c r="T33" t="n">
-        <v>0.01577010449583528</v>
+        <v>0.023314874408194</v>
       </c>
       <c r="U33" t="n">
-        <v>0.02412089826765769</v>
+        <v>0.02052905189638906</v>
       </c>
       <c r="V33" t="n">
-        <v>0.008798785252329851</v>
+        <v>0.008692206022018971</v>
       </c>
       <c r="W33" t="n">
-        <v>0.01425303978700799</v>
+        <v>0.01495124525637704</v>
       </c>
       <c r="X33" t="n">
-        <v>0.007886086965499323</v>
+        <v>0.007837770432662943</v>
       </c>
     </row>
     <row r="34">
@@ -3131,61 +3131,61 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5350531219152354</v>
+        <v>0.5348911130605229</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4497671777617613</v>
+        <v>0.5384668528672936</v>
       </c>
       <c r="M34" t="n">
-        <v>4.263995602912937</v>
+        <v>4.266762406485488</v>
       </c>
       <c r="N34" t="n">
-        <v>4.286052599309091</v>
+        <v>4.312442066410434</v>
       </c>
       <c r="O34" t="n">
-        <v>0.005327415999576042</v>
+        <v>0.00629562701552152</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01468639974602328</v>
+        <v>0.01685103135998725</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.00299204878747737</v>
+        <v>0.003609084823573983</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01477537078025103</v>
+        <v>0.0175965156972246</v>
       </c>
       <c r="S34" t="n">
-        <v>0.008485399023264808</v>
+        <v>0.01047946919245789</v>
       </c>
       <c r="T34" t="n">
-        <v>0.008064321238122247</v>
+        <v>0.009999946561555709</v>
       </c>
       <c r="U34" t="n">
-        <v>0.0557478055123624</v>
+        <v>0.08038445959465043</v>
       </c>
       <c r="V34" t="n">
-        <v>0.005681397228123481</v>
+        <v>0.005150928961116965</v>
       </c>
       <c r="W34" t="n">
-        <v>0.01887525403640121</v>
+        <v>0.02268251891265146</v>
       </c>
       <c r="X34" t="n">
-        <v>0.007357860210382738</v>
+        <v>0.008952354075695538</v>
       </c>
     </row>
     <row r="35">
@@ -3211,61 +3211,61 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3019491379002337</v>
+        <v>0.2505782405517368</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2474307506948766</v>
+        <v>0.247716577227182</v>
       </c>
       <c r="M35" t="n">
-        <v>4.049560543950747</v>
+        <v>4.045560608437414</v>
       </c>
       <c r="N35" t="n">
-        <v>4.156376139907135</v>
+        <v>4.15113985373848</v>
       </c>
       <c r="O35" t="n">
-        <v>0.002523941268916878</v>
+        <v>0.003337612813928194</v>
       </c>
       <c r="P35" t="n">
-        <v>0.06032815418094361</v>
+        <v>0.07168665982796048</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0006042484939012196</v>
+        <v>0.000571144027703687</v>
       </c>
       <c r="R35" t="n">
-        <v>0.004779303674939503</v>
+        <v>0.004608573958777616</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0009526234589107368</v>
+        <v>0.0009309640553607385</v>
       </c>
       <c r="T35" t="n">
-        <v>0.01062014581763511</v>
+        <v>0.01476533165735805</v>
       </c>
       <c r="U35" t="n">
-        <v>21.31919935089066</v>
+        <v>31.47101991523071</v>
       </c>
       <c r="V35" t="n">
-        <v>0.00224662381008793</v>
+        <v>0.002167130473552537</v>
       </c>
       <c r="W35" t="n">
-        <v>0.01873468174416219</v>
+        <v>0.01544151875593386</v>
       </c>
       <c r="X35" t="n">
-        <v>0.002611807417507275</v>
+        <v>0.002520839668937755</v>
       </c>
     </row>
     <row r="36">
@@ -3291,61 +3291,61 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4306133506575378</v>
+        <v>0.3956792038623253</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3952362728840799</v>
+        <v>0.3771774987149752</v>
       </c>
       <c r="M36" t="n">
-        <v>4.307865273041947</v>
+        <v>4.298761590070961</v>
       </c>
       <c r="N36" t="n">
-        <v>4.321572623486516</v>
+        <v>4.314521842931012</v>
       </c>
       <c r="O36" t="n">
-        <v>0.001343523339487707</v>
+        <v>0.001469854402202507</v>
       </c>
       <c r="P36" t="n">
-        <v>0.002753977254333692</v>
+        <v>0.002620853217931327</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0004271144016157931</v>
+        <v>0.0003958491160124328</v>
       </c>
       <c r="R36" t="n">
-        <v>0.00193282878989933</v>
+        <v>0.001820364886196814</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001308574399388756</v>
+        <v>0.001239223763040016</v>
       </c>
       <c r="T36" t="n">
-        <v>0.003546840140929287</v>
+        <v>0.004030738006360441</v>
       </c>
       <c r="U36" t="n">
-        <v>0.006142816038114112</v>
+        <v>0.00577013456384589</v>
       </c>
       <c r="V36" t="n">
-        <v>0.002583706314445259</v>
+        <v>0.002558983121866279</v>
       </c>
       <c r="W36" t="n">
-        <v>0.003628160873148946</v>
+        <v>0.003589935731194455</v>
       </c>
       <c r="X36" t="n">
-        <v>0.004515743683529813</v>
+        <v>0.004475253503331811</v>
       </c>
     </row>
     <row r="37">
@@ -3371,61 +3371,61 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1032759135620988</v>
+        <v>0.05738019622196385</v>
       </c>
       <c r="L37" t="n">
-        <v>0.105288088556548</v>
+        <v>0.07190125053007634</v>
       </c>
       <c r="M37" t="n">
-        <v>4.230764125716685</v>
+        <v>4.219329310499894</v>
       </c>
       <c r="N37" t="n">
-        <v>4.263240945631649</v>
+        <v>4.254748164104436</v>
       </c>
       <c r="O37" t="n">
-        <v>0.007667241941911612</v>
+        <v>0.01419430751719529</v>
       </c>
       <c r="P37" t="n">
-        <v>0.003373473473283984</v>
+        <v>0.003970387760790649</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.001128822814805678</v>
+        <v>0.00110150966213122</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0008424215255491023</v>
+        <v>0.0007391393914700466</v>
       </c>
       <c r="S37" t="n">
-        <v>0.002261621751080345</v>
+        <v>0.001948695408616885</v>
       </c>
       <c r="T37" t="n">
-        <v>0.02824965751043103</v>
+        <v>0.06175502143646608</v>
       </c>
       <c r="U37" t="n">
-        <v>0.009400509936786258</v>
+        <v>0.01516786162684424</v>
       </c>
       <c r="V37" t="n">
-        <v>0.003042171779284847</v>
+        <v>0.002950268865545247</v>
       </c>
       <c r="W37" t="n">
-        <v>0.002556232092759398</v>
+        <v>0.002462149102474331</v>
       </c>
       <c r="X37" t="n">
-        <v>0.005709979705498007</v>
+        <v>0.005000771704942957</v>
       </c>
     </row>
     <row r="38">
@@ -3451,61 +3451,61 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1416438943560188</v>
+        <v>0.08867237739422326</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1093720223530449</v>
+        <v>0.07320842366714349</v>
       </c>
       <c r="M38" t="n">
-        <v>4.113546643685265</v>
+        <v>4.086901387408154</v>
       </c>
       <c r="N38" t="n">
-        <v>4.195688196265935</v>
+        <v>4.186769011306909</v>
       </c>
       <c r="O38" t="n">
-        <v>0.009403217904520443</v>
+        <v>0.01808078005569926</v>
       </c>
       <c r="P38" t="n">
-        <v>0.002589265482107528</v>
+        <v>0.004211454220738628</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0006754920509172869</v>
+        <v>0.0006318491899226312</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0004656697738782062</v>
+        <v>0.000364327607185966</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0003975030949684453</v>
+        <v>1.513315947776252e-05</v>
       </c>
       <c r="T38" t="n">
-        <v>0.0314208676008576</v>
+        <v>0.06931498535894959</v>
       </c>
       <c r="U38" t="n">
-        <v>0.009153900516608731</v>
+        <v>0.01784522996214306</v>
       </c>
       <c r="V38" t="n">
-        <v>0.002435890371761852</v>
+        <v>0.002354218943057131</v>
       </c>
       <c r="W38" t="n">
-        <v>0.002125676676037555</v>
+        <v>0.002050240595088031</v>
       </c>
       <c r="X38" t="n">
-        <v>0.003144106513486889</v>
+        <v>0.002561366906263916</v>
       </c>
     </row>
     <row r="39">
@@ -3531,61 +3531,61 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1514776863482813</v>
+        <v>0.09605755582229301</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1340398372572274</v>
+        <v>0.09759740726244502</v>
       </c>
       <c r="M39" t="n">
-        <v>4.258531293425802</v>
+        <v>4.239319110069875</v>
       </c>
       <c r="N39" t="n">
-        <v>4.266069201335666</v>
+        <v>4.257443659965783</v>
       </c>
       <c r="O39" t="n">
-        <v>0.006493221980259241</v>
+        <v>0.01072037594928983</v>
       </c>
       <c r="P39" t="n">
-        <v>0.002046783212853728</v>
+        <v>0.00196295982645286</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.001058373386804991</v>
+        <v>0.001027527987212673</v>
       </c>
       <c r="R39" t="n">
-        <v>0.002328310731240582</v>
+        <v>0.002113319065201823</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001423219936509659</v>
+        <v>0.001326701221836573</v>
       </c>
       <c r="T39" t="n">
-        <v>0.01689977535532027</v>
+        <v>0.03135488703786923</v>
       </c>
       <c r="U39" t="n">
-        <v>0.009748034530251472</v>
+        <v>0.01333831421713467</v>
       </c>
       <c r="V39" t="n">
-        <v>0.002831396688727956</v>
+        <v>0.00278094164293222</v>
       </c>
       <c r="W39" t="n">
-        <v>0.004037135450186052</v>
+        <v>0.003892841141048429</v>
       </c>
       <c r="X39" t="n">
-        <v>0.00302366556319029</v>
+        <v>0.002971323793524849</v>
       </c>
     </row>
     <row r="40">
@@ -3611,61 +3611,61 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.369449111753018</v>
+        <v>0.3245675201964789</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4154719928634318</v>
+        <v>0.4118938711176564</v>
       </c>
       <c r="M40" t="n">
-        <v>4.291879477204492</v>
+        <v>4.31638491374612</v>
       </c>
       <c r="N40" t="n">
-        <v>4.519316918206653</v>
+        <v>4.514996271922406</v>
       </c>
       <c r="O40" t="n">
-        <v>0.004343395176316576</v>
+        <v>0.004814700882951922</v>
       </c>
       <c r="P40" t="n">
-        <v>0.00275699285003071</v>
+        <v>0.002433377514510756</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.002570057364652736</v>
+        <v>0.002507727756436091</v>
       </c>
       <c r="R40" t="n">
-        <v>0.002587362474014898</v>
+        <v>0.002528847225288386</v>
       </c>
       <c r="S40" t="n">
-        <v>0.06760726698865352</v>
+        <v>0.06035065382371903</v>
       </c>
       <c r="T40" t="n">
-        <v>0.008823276208000433</v>
+        <v>0.01044834893024696</v>
       </c>
       <c r="U40" t="n">
-        <v>0.004059732168570239</v>
+        <v>0.003746213489123587</v>
       </c>
       <c r="V40" t="n">
-        <v>0.005048471207835985</v>
+        <v>0.004973348343547456</v>
       </c>
       <c r="W40" t="n">
-        <v>0.004129174269690187</v>
+        <v>0.004188706335114709</v>
       </c>
       <c r="X40" t="n">
-        <v>0.3157448763453544</v>
+        <v>0.2820917833724184</v>
       </c>
     </row>
     <row r="41">
@@ -3691,61 +3691,61 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2579668639842531</v>
+        <v>0.1960310268779012</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2828060281350324</v>
+        <v>0.2440452282739568</v>
       </c>
       <c r="M41" t="n">
-        <v>4.436658070637798</v>
+        <v>4.444024655632611</v>
       </c>
       <c r="N41" t="n">
-        <v>4.507114060793552</v>
+        <v>4.504187696775265</v>
       </c>
       <c r="O41" t="n">
-        <v>0.00192674260487236</v>
+        <v>0.002338318429466643</v>
       </c>
       <c r="P41" t="n">
-        <v>0.003097238040763322</v>
+        <v>0.002594304777076386</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.0009940943398252147</v>
+        <v>0.0009655036975778467</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0009567182117475711</v>
+        <v>0.0008835895695120642</v>
       </c>
       <c r="S41" t="n">
-        <v>0.003921441164234186</v>
+        <v>0.003625648474620262</v>
       </c>
       <c r="T41" t="n">
-        <v>0.004780961990616349</v>
+        <v>0.006351938420116927</v>
       </c>
       <c r="U41" t="n">
-        <v>0.005278800118553847</v>
+        <v>0.004712603614081622</v>
       </c>
       <c r="V41" t="n">
-        <v>0.002241589427450708</v>
+        <v>0.002199045467974372</v>
       </c>
       <c r="W41" t="n">
-        <v>0.002146721513542883</v>
+        <v>0.002080479392765767</v>
       </c>
       <c r="X41" t="n">
-        <v>0.006902755690205851</v>
+        <v>0.00652559040025954</v>
       </c>
     </row>
     <row r="42">
@@ -3771,61 +3771,61 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3170323710220794</v>
+        <v>0.2509391170687325</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3994897305376252</v>
+        <v>0.3542623710802913</v>
       </c>
       <c r="M42" t="n">
-        <v>4.517983722179811</v>
+        <v>4.41672374136586</v>
       </c>
       <c r="N42" t="n">
-        <v>4.483456920706354</v>
+        <v>4.454935633917987</v>
       </c>
       <c r="O42" t="n">
-        <v>0.005262322057054487</v>
+        <v>0.006230201891398958</v>
       </c>
       <c r="P42" t="n">
-        <v>0.003751669231455244</v>
+        <v>0.002626640639557112</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.00422829204637201</v>
+        <v>0.003897268389341374</v>
       </c>
       <c r="R42" t="n">
-        <v>0.003011072868032726</v>
+        <v>0.002806490660117976</v>
       </c>
       <c r="S42" t="n">
-        <v>0.003473240025523957</v>
+        <v>0.0114140369663968</v>
       </c>
       <c r="T42" t="n">
-        <v>0.02365289516650815</v>
+        <v>0.03954123015637864</v>
       </c>
       <c r="U42" t="n">
-        <v>0.01562617235200352</v>
+        <v>0.01154140968778515</v>
       </c>
       <c r="V42" t="n">
-        <v>0.0123243162194725</v>
+        <v>0.01057745512854912</v>
       </c>
       <c r="W42" t="n">
-        <v>0.01287070091062401</v>
+        <v>0.006334336323043348</v>
       </c>
       <c r="X42" t="n">
-        <v>3.849756211050409</v>
+        <v>17.28081695375366</v>
       </c>
     </row>
     <row r="43">
@@ -3851,61 +3851,61 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2387871798140294</v>
+        <v>0.184253646780577</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3355226834697559</v>
+        <v>0.2869012964917135</v>
       </c>
       <c r="M43" t="n">
-        <v>3.927442132088704</v>
+        <v>3.920875439924891</v>
       </c>
       <c r="N43" t="n">
-        <v>4.245341406910314</v>
+        <v>4.230025302991455</v>
       </c>
       <c r="O43" t="n">
-        <v>0.03083087119661809</v>
+        <v>0.05221318400038303</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0136636998023586</v>
+        <v>0.01430340017512301</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.01660582695498348</v>
+        <v>0.01466794749448137</v>
       </c>
       <c r="R43" t="n">
-        <v>0.02035039721787303</v>
+        <v>0.01587906752034718</v>
       </c>
       <c r="S43" t="n">
-        <v>0.0615337612807088</v>
+        <v>0.05723483725379255</v>
       </c>
       <c r="T43" t="n">
-        <v>0.06946921823193013</v>
+        <v>0.1545569618116712</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02270777734303643</v>
+        <v>0.02532042522549574</v>
       </c>
       <c r="V43" t="n">
-        <v>0.03640213347729687</v>
+        <v>0.03026388419632726</v>
       </c>
       <c r="W43" t="n">
-        <v>0.04297741874501491</v>
+        <v>0.0361208656301085</v>
       </c>
       <c r="X43" t="n">
-        <v>0.1664054808596388</v>
+        <v>0.1546624018944377</v>
       </c>
     </row>
     <row r="44">
@@ -3931,61 +3931,61 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1743546614482898</v>
+        <v>0.1161247165757327</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3610732774323228</v>
+        <v>0.2746994828953634</v>
       </c>
       <c r="M44" t="n">
-        <v>4.252007996567885</v>
+        <v>4.226110669456893</v>
       </c>
       <c r="N44" t="n">
-        <v>4.379586724816082</v>
+        <v>4.359696884688503</v>
       </c>
       <c r="O44" t="n">
-        <v>0.05943180072319394</v>
+        <v>0.09695824472565918</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02258796355990136</v>
+        <v>0.02927531683909404</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.02157829855557556</v>
+        <v>0.01724321576425785</v>
       </c>
       <c r="R44" t="n">
-        <v>0.01165903541634562</v>
+        <v>0.009785859000917108</v>
       </c>
       <c r="S44" t="n">
-        <v>0.02252466555922277</v>
+        <v>0.01783441789055376</v>
       </c>
       <c r="T44" t="n">
-        <v>0.1751135108474007</v>
+        <v>0.3418325628441926</v>
       </c>
       <c r="U44" t="n">
-        <v>0.04189371151768493</v>
+        <v>0.07891293966683598</v>
       </c>
       <c r="V44" t="n">
-        <v>0.04916033192741588</v>
+        <v>0.03566762918147429</v>
       </c>
       <c r="W44" t="n">
-        <v>0.02319956777261208</v>
+        <v>0.01979541483860568</v>
       </c>
       <c r="X44" t="n">
-        <v>0.04696270116222825</v>
+        <v>0.03676803080609439</v>
       </c>
     </row>
     <row r="45">
@@ -4011,61 +4011,61 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3961005288343256</v>
+        <v>0.3561715337841546</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2479943294578413</v>
+        <v>0.4598071986904772</v>
       </c>
       <c r="M45" t="n">
-        <v>4.214350986480778</v>
+        <v>4.204683775347685</v>
       </c>
       <c r="N45" t="n">
-        <v>4.321283307910669</v>
+        <v>4.424013673050669</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1307536841507036</v>
+        <v>0.1557151657858743</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1320966209382474</v>
+        <v>0.1388645884401747</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.05081882791349295</v>
+        <v>0.05061058147934436</v>
       </c>
       <c r="R45" t="n">
-        <v>0.09173536452010415</v>
+        <v>0.09297534242724799</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1078988148880706</v>
+        <v>0.1159768802417834</v>
       </c>
       <c r="T45" t="n">
-        <v>0.6328950612962737</v>
+        <v>0.9372508569352602</v>
       </c>
       <c r="U45" t="n">
-        <v>0.4249006086480794</v>
+        <v>0.5121542114541249</v>
       </c>
       <c r="V45" t="n">
-        <v>0.151324651590732</v>
+        <v>0.1497409404427728</v>
       </c>
       <c r="W45" t="n">
-        <v>0.2474850442376834</v>
+        <v>0.2681851975479116</v>
       </c>
       <c r="X45" t="n">
-        <v>0.3929057540413145</v>
+        <v>0.4465962169503613</v>
       </c>
     </row>
     <row r="46">
@@ -4091,61 +4091,61 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4197523519087317</v>
+        <v>0.4073750266228692</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3537994247664817</v>
+        <v>0.4880065708911719</v>
       </c>
       <c r="M46" t="n">
-        <v>3.774562388265622</v>
+        <v>3.814004562068153</v>
       </c>
       <c r="N46" t="n">
-        <v>4.475097579018535</v>
+        <v>4.469350610938019</v>
       </c>
       <c r="O46" t="n">
-        <v>0.06990515626302188</v>
+        <v>0.07682959994522309</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0447362377903212</v>
+        <v>0.04836617575629115</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.02429470085322225</v>
+        <v>0.0248778324833259</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0363765242040655</v>
+        <v>0.03873490004149029</v>
       </c>
       <c r="S46" t="n">
-        <v>0.1859470277317496</v>
+        <v>0.1786212383203389</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1891339483173926</v>
+        <v>0.2187012618047699</v>
       </c>
       <c r="U46" t="n">
-        <v>0.08991401939022291</v>
+        <v>0.1005000216569451</v>
       </c>
       <c r="V46" t="n">
-        <v>0.0464486439283922</v>
+        <v>0.04509803799823041</v>
       </c>
       <c r="W46" t="n">
-        <v>0.05656817999001105</v>
+        <v>0.0619766858571695</v>
       </c>
       <c r="X46" t="n">
-        <v>2.115862403045977</v>
+        <v>1.804040518948512</v>
       </c>
     </row>
     <row r="47">
@@ -4171,61 +4171,61 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2493695583752376</v>
+        <v>0.1887746212355711</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3343697951216354</v>
+        <v>0.2874290224747945</v>
       </c>
       <c r="M47" t="n">
-        <v>4.220558446554917</v>
+        <v>4.185310192182019</v>
       </c>
       <c r="N47" t="n">
-        <v>4.341455675135808</v>
+        <v>4.328583899228017</v>
       </c>
       <c r="O47" t="n">
-        <v>0.04722494907936614</v>
+        <v>0.07110940241914274</v>
       </c>
       <c r="P47" t="n">
-        <v>0.02084494714261795</v>
+        <v>0.02770484688983762</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.0177498432008436</v>
+        <v>0.0150711770579044</v>
       </c>
       <c r="R47" t="n">
-        <v>0.01565835932171035</v>
+        <v>0.0134730992980786</v>
       </c>
       <c r="S47" t="n">
-        <v>0.02308905151123523</v>
+        <v>0.019428418788142</v>
       </c>
       <c r="T47" t="n">
-        <v>0.1186555869560494</v>
+        <v>0.2133976947131692</v>
       </c>
       <c r="U47" t="n">
-        <v>0.03866223272704897</v>
+        <v>0.06748491365311077</v>
       </c>
       <c r="V47" t="n">
-        <v>0.03963500892286444</v>
+        <v>0.03070221996367363</v>
       </c>
       <c r="W47" t="n">
-        <v>0.02865151977507392</v>
+        <v>0.02444713432633894</v>
       </c>
       <c r="X47" t="n">
-        <v>0.04388326360448622</v>
+        <v>0.03594619863005422</v>
       </c>
     </row>
     <row r="48">
@@ -4251,61 +4251,61 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.109062118721277</v>
+        <v>0.06767257822732965</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4844389589843668</v>
+        <v>0.3444655170478663</v>
       </c>
       <c r="M48" t="n">
-        <v>3.575232101365941</v>
+        <v>3.655465587484483</v>
       </c>
       <c r="N48" t="n">
-        <v>4.355927683725671</v>
+        <v>4.377152554950563</v>
       </c>
       <c r="O48" t="n">
-        <v>0.03702363992438523</v>
+        <v>0.1270028619427106</v>
       </c>
       <c r="P48" t="n">
-        <v>0.05708986194302317</v>
+        <v>0.09873750319455882</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.06292346146347325</v>
+        <v>0.03592619996030982</v>
       </c>
       <c r="R48" t="n">
-        <v>0.0488321549946007</v>
+        <v>0.0223041059189317</v>
       </c>
       <c r="S48" t="n">
-        <v>0.2381958633347792</v>
+        <v>0.135429311126786</v>
       </c>
       <c r="T48" t="n">
-        <v>0.09799957050706212</v>
+        <v>0.5735611188183101</v>
       </c>
       <c r="U48" t="n">
-        <v>0.12193229432994</v>
+        <v>0.36919788510868</v>
       </c>
       <c r="V48" t="n">
-        <v>0.1366994689081784</v>
+        <v>0.08415747515012176</v>
       </c>
       <c r="W48" t="n">
-        <v>0.08238586919110011</v>
+        <v>0.07474960721771885</v>
       </c>
       <c r="X48" t="n">
-        <v>4.820433676246771</v>
+        <v>1.433990799904918</v>
       </c>
     </row>
     <row r="49">
@@ -4331,61 +4331,61 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3626999688036405</v>
+        <v>0.3236571036150679</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4632387050699576</v>
+        <v>0.4686144102921178</v>
       </c>
       <c r="M49" t="n">
-        <v>4.039369874984286</v>
+        <v>4.059016345835413</v>
       </c>
       <c r="N49" t="n">
-        <v>4.389543164419961</v>
+        <v>4.382834935369007</v>
       </c>
       <c r="O49" t="n">
-        <v>0.02015473646118817</v>
+        <v>0.02192113966028977</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01237905427025131</v>
+        <v>0.0122837639981582</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.01860104134347483</v>
+        <v>0.01827357291708274</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01792447480202259</v>
+        <v>0.01803190180433827</v>
       </c>
       <c r="S49" t="n">
-        <v>0.09060877003094345</v>
+        <v>0.08645827567644777</v>
       </c>
       <c r="T49" t="n">
-        <v>0.03979412680634243</v>
+        <v>0.04646816075417215</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01619431776433744</v>
+        <v>0.01620464291260096</v>
       </c>
       <c r="V49" t="n">
-        <v>0.04072468555156591</v>
+        <v>0.04043125544948525</v>
       </c>
       <c r="W49" t="n">
-        <v>0.02776088375115171</v>
+        <v>0.02941485181432486</v>
       </c>
       <c r="X49" t="n">
-        <v>0.3081305999573403</v>
+        <v>0.2873370510662619</v>
       </c>
     </row>
     <row r="50">
@@ -4411,61 +4411,61 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.509975097271933</v>
+        <v>0.5001414823415646</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5510567329931866</v>
+        <v>0.5577757949470938</v>
       </c>
       <c r="M50" t="n">
-        <v>4.291212719785222</v>
+        <v>4.295513413439029</v>
       </c>
       <c r="N50" t="n">
-        <v>4.504047402474733</v>
+        <v>4.457044878795037</v>
       </c>
       <c r="O50" t="n">
-        <v>0.06811326347880989</v>
+        <v>0.06788926081304565</v>
       </c>
       <c r="P50" t="n">
-        <v>0.06354042613351439</v>
+        <v>0.06368326268118228</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.06035715160801244</v>
+        <v>0.06115764601149682</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0330140599867615</v>
+        <v>0.03428496332131594</v>
       </c>
       <c r="S50" t="n">
-        <v>0.005333021605786354</v>
+        <v>0.01154321531393496</v>
       </c>
       <c r="T50" t="n">
-        <v>0.22100307175416</v>
+        <v>0.2593573616478965</v>
       </c>
       <c r="U50" t="n">
-        <v>0.2020218657455441</v>
+        <v>0.2522866336263648</v>
       </c>
       <c r="V50" t="n">
-        <v>0.1298128226676996</v>
+        <v>0.2198777376994573</v>
       </c>
       <c r="W50" t="n">
-        <v>0.05767550358487186</v>
+        <v>0.1318869145564563</v>
       </c>
       <c r="X50" t="n">
-        <v>9.876632758716937</v>
+        <v>16.03225845867846</v>
       </c>
     </row>
     <row r="51">
@@ -4491,61 +4491,61 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4767246818589526</v>
+        <v>0.4746629412539786</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5522639707573709</v>
+        <v>0.5586512994732975</v>
       </c>
       <c r="M51" t="n">
-        <v>3.852084868275818</v>
+        <v>3.848875145161648</v>
       </c>
       <c r="N51" t="n">
-        <v>4.429624212899792</v>
+        <v>4.430374646935658</v>
       </c>
       <c r="O51" t="n">
-        <v>0.05491846238935823</v>
+        <v>0.05471086747587899</v>
       </c>
       <c r="P51" t="n">
-        <v>0.04117347659418068</v>
+        <v>0.04132291046026035</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1264695062825598</v>
+        <v>0.1282684037246763</v>
       </c>
       <c r="R51" t="n">
-        <v>0.06297349632791406</v>
+        <v>0.06379599648539155</v>
       </c>
       <c r="S51" t="n">
-        <v>0.2140358340015852</v>
+        <v>0.2176649002617974</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1333764015336087</v>
+        <v>0.1325736777540877</v>
       </c>
       <c r="U51" t="n">
-        <v>0.08217932098259809</v>
+        <v>0.0824556483190052</v>
       </c>
       <c r="V51" t="n">
-        <v>0.2325102286839425</v>
+        <v>0.2290102194938922</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1170833451957221</v>
+        <v>0.1194794949804297</v>
       </c>
       <c r="X51" t="n">
-        <v>2.349713694515988</v>
+        <v>2.407352494974069</v>
       </c>
     </row>
     <row r="52">
@@ -4571,61 +4571,61 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.157761930875372</v>
+        <v>0.101465410040746</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2333175373332652</v>
+        <v>0.1832309999901167</v>
       </c>
       <c r="M52" t="n">
-        <v>4.292754697312241</v>
+        <v>4.284078512333842</v>
       </c>
       <c r="N52" t="n">
-        <v>4.284848173608673</v>
+        <v>4.269507928507823</v>
       </c>
       <c r="O52" t="n">
-        <v>0.02168766463117145</v>
+        <v>0.03164884833657914</v>
       </c>
       <c r="P52" t="n">
-        <v>0.009439895818457951</v>
+        <v>0.01072562051701149</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.008160915449791941</v>
+        <v>0.007621309862449675</v>
       </c>
       <c r="R52" t="n">
-        <v>0.004617006876690318</v>
+        <v>0.003781409868006571</v>
       </c>
       <c r="S52" t="n">
-        <v>0.01393490247454197</v>
+        <v>0.01078147063485251</v>
       </c>
       <c r="T52" t="n">
-        <v>0.0540949132481233</v>
+        <v>0.09460701130040967</v>
       </c>
       <c r="U52" t="n">
-        <v>0.02182633007498416</v>
+        <v>0.03021695865445212</v>
       </c>
       <c r="V52" t="n">
-        <v>0.01592965560247066</v>
+        <v>0.01460165865356912</v>
       </c>
       <c r="W52" t="n">
-        <v>0.01230258960988904</v>
+        <v>0.01128793644165299</v>
       </c>
       <c r="X52" t="n">
-        <v>0.03957910897396508</v>
+        <v>0.03366380531981379</v>
       </c>
     </row>
     <row r="53">
@@ -4651,61 +4651,61 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3306984100273074</v>
+        <v>0.2727378027638814</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2217652418478735</v>
+        <v>0.2724215023286474</v>
       </c>
       <c r="M53" t="n">
-        <v>4.388506524434447</v>
+        <v>4.35109846563273</v>
       </c>
       <c r="N53" t="n">
-        <v>4.433878034578161</v>
+        <v>4.43548326789218</v>
       </c>
       <c r="O53" t="n">
-        <v>0.03773171920031353</v>
+        <v>0.05422302654978829</v>
       </c>
       <c r="P53" t="n">
-        <v>0.02216863315702666</v>
+        <v>0.02504921565826318</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.009369705110336168</v>
+        <v>0.009120558779230275</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02188702540227282</v>
+        <v>0.02152047579568387</v>
       </c>
       <c r="S53" t="n">
-        <v>0.06792457934647343</v>
+        <v>0.0627282334772222</v>
       </c>
       <c r="T53" t="n">
-        <v>0.07936928765021489</v>
+        <v>0.1381598229581298</v>
       </c>
       <c r="U53" t="n">
-        <v>0.03713849859144589</v>
+        <v>0.04899978974172908</v>
       </c>
       <c r="V53" t="n">
-        <v>0.01637342217525893</v>
+        <v>0.01597795871589956</v>
       </c>
       <c r="W53" t="n">
-        <v>0.03699585122714485</v>
+        <v>0.03832787774158337</v>
       </c>
       <c r="X53" t="n">
-        <v>0.08374183778681031</v>
+        <v>0.08041437243331148</v>
       </c>
     </row>
     <row r="54">
@@ -4731,61 +4731,61 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2248167586008439</v>
+        <v>0.1659250005802807</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4317427166752927</v>
+        <v>0.3933881077293672</v>
       </c>
       <c r="M54" t="n">
-        <v>4.171678408154621</v>
+        <v>4.164746083868372</v>
       </c>
       <c r="N54" t="n">
-        <v>4.310947938073172</v>
+        <v>4.286669372154264</v>
       </c>
       <c r="O54" t="n">
-        <v>0.03451144435435846</v>
+        <v>0.04347550357456944</v>
       </c>
       <c r="P54" t="n">
-        <v>0.009527280442766852</v>
+        <v>0.009571687757120325</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.02262299446918152</v>
+        <v>0.02021202862744639</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009788120828992693</v>
+        <v>0.008367844727373203</v>
       </c>
       <c r="S54" t="n">
-        <v>0.02405223594047966</v>
+        <v>0.02136512502590521</v>
       </c>
       <c r="T54" t="n">
-        <v>0.0894037953053019</v>
+        <v>0.1294398679730743</v>
       </c>
       <c r="U54" t="n">
-        <v>0.01657193792019307</v>
+        <v>0.01681693199477396</v>
       </c>
       <c r="V54" t="n">
-        <v>0.05313633896995817</v>
+        <v>0.04692595518978271</v>
       </c>
       <c r="W54" t="n">
-        <v>0.01912928457290105</v>
+        <v>0.01940320137480547</v>
       </c>
       <c r="X54" t="n">
-        <v>0.04495289356130284</v>
+        <v>0.04191338405018501</v>
       </c>
     </row>
     <row r="55">
@@ -4811,61 +4811,61 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2017005542879495</v>
+        <v>0.1407164034552979</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4744089944278345</v>
+        <v>0.4855743751268248</v>
       </c>
       <c r="M55" t="n">
-        <v>4.462283023203961</v>
+        <v>4.488546076885461</v>
       </c>
       <c r="N55" t="n">
-        <v>4.393522777712328</v>
+        <v>4.394086995407828</v>
       </c>
       <c r="O55" t="n">
-        <v>0.02211484919909035</v>
+        <v>0.0231282969861582</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01007707984679511</v>
+        <v>0.01001354159541686</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.03116002205003729</v>
+        <v>0.03710343699957081</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01554485627590557</v>
+        <v>0.01592966540292588</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0162846078576839</v>
+        <v>0.01693666034215913</v>
       </c>
       <c r="T55" t="n">
-        <v>0.04990557990879467</v>
+        <v>0.05528534341396785</v>
       </c>
       <c r="U55" t="n">
-        <v>0.0166339879650558</v>
+        <v>0.01653084838702444</v>
       </c>
       <c r="V55" t="n">
-        <v>0.05906444679098795</v>
+        <v>0.06798624531033699</v>
       </c>
       <c r="W55" t="n">
-        <v>0.02105874376837123</v>
+        <v>0.02125885993797498</v>
       </c>
       <c r="X55" t="n">
-        <v>0.02563505396344248</v>
+        <v>0.02445447310727311</v>
       </c>
     </row>
     <row r="56">
@@ -4891,61 +4891,61 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2039298221414741</v>
+        <v>0.1460704737966806</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3225291753110692</v>
+        <v>0.2351975054111471</v>
       </c>
       <c r="M56" t="n">
-        <v>3.981252851815453</v>
+        <v>3.92679468727763</v>
       </c>
       <c r="N56" t="n">
-        <v>4.30712946662735</v>
+        <v>4.297981081719553</v>
       </c>
       <c r="O56" t="n">
-        <v>0.02623284382628321</v>
+        <v>0.04691155749775006</v>
       </c>
       <c r="P56" t="n">
-        <v>0.01234599096944209</v>
+        <v>0.01754630138991416</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.01361231652188452</v>
+        <v>0.01039009808029463</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01291216428751192</v>
+        <v>0.01089843856978162</v>
       </c>
       <c r="S56" t="n">
-        <v>0.04266136529566093</v>
+        <v>0.04095224224370835</v>
       </c>
       <c r="T56" t="n">
-        <v>0.06351380760775961</v>
+        <v>0.141546383456622</v>
       </c>
       <c r="U56" t="n">
-        <v>0.02360128902844759</v>
+        <v>0.04586335934233195</v>
       </c>
       <c r="V56" t="n">
-        <v>0.02963555531010365</v>
+        <v>0.02056490507558185</v>
       </c>
       <c r="W56" t="n">
-        <v>0.02318867627299311</v>
+        <v>0.0195862729450151</v>
       </c>
       <c r="X56" t="n">
-        <v>0.107608343986451</v>
+        <v>0.1054397614063806</v>
       </c>
     </row>
     <row r="57">
@@ -4971,61 +4971,61 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3806411666965068</v>
+        <v>0.3372330102865788</v>
       </c>
       <c r="L57" t="n">
-        <v>0.447059970211117</v>
+        <v>0.4424917996776094</v>
       </c>
       <c r="M57" t="n">
-        <v>4.256768970266466</v>
+        <v>4.259702116978529</v>
       </c>
       <c r="N57" t="n">
-        <v>4.367587060948538</v>
+        <v>4.360492222091802</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02703240398254442</v>
+        <v>0.03001506794234124</v>
       </c>
       <c r="P57" t="n">
-        <v>0.01018010379005899</v>
+        <v>0.01075414859172882</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01544971659160706</v>
+        <v>0.01458239889799871</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01359616928404648</v>
+        <v>0.01327408214149144</v>
       </c>
       <c r="S57" t="n">
-        <v>0.02077661567532103</v>
+        <v>0.01974595170503979</v>
       </c>
       <c r="T57" t="n">
-        <v>0.05679796409358333</v>
+        <v>0.06637711045979706</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01694821873466503</v>
+        <v>0.01897269308462377</v>
       </c>
       <c r="V57" t="n">
-        <v>0.03208324969321535</v>
+        <v>0.03030687108507573</v>
       </c>
       <c r="W57" t="n">
-        <v>0.0200225501218064</v>
+        <v>0.02062594924265041</v>
       </c>
       <c r="X57" t="n">
-        <v>0.03237617380169238</v>
+        <v>0.03155294837477465</v>
       </c>
     </row>
     <row r="58">
@@ -5051,61 +5051,61 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2253496777622122</v>
+        <v>0.1681963868140562</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5219633775109136</v>
+        <v>0.5204575355029258</v>
       </c>
       <c r="M58" t="n">
-        <v>4.133633433248462</v>
+        <v>4.153505266863479</v>
       </c>
       <c r="N58" t="n">
-        <v>4.450601643647527</v>
+        <v>4.447654902378698</v>
       </c>
       <c r="O58" t="n">
-        <v>0.06845660356213161</v>
+        <v>0.07449547751992722</v>
       </c>
       <c r="P58" t="n">
-        <v>0.0101151131333709</v>
+        <v>0.009874369450670984</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.05143852212877134</v>
+        <v>0.05410165528266869</v>
       </c>
       <c r="R58" t="n">
-        <v>0.009591726525317401</v>
+        <v>0.009260729998083759</v>
       </c>
       <c r="S58" t="n">
-        <v>0.05178520361383275</v>
+        <v>0.05015964373695932</v>
       </c>
       <c r="T58" t="n">
-        <v>0.1918666635780459</v>
+        <v>0.2239443545518275</v>
       </c>
       <c r="U58" t="n">
-        <v>0.01805807566127462</v>
+        <v>0.01792270403620497</v>
       </c>
       <c r="V58" t="n">
-        <v>0.1442198232992784</v>
+        <v>0.157378323742732</v>
       </c>
       <c r="W58" t="n">
-        <v>0.01879132828635423</v>
+        <v>0.01936396854592165</v>
       </c>
       <c r="X58" t="n">
-        <v>0.1122213465368152</v>
+        <v>0.1124219028865717</v>
       </c>
     </row>
     <row r="59">
@@ -5131,61 +5131,61 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4654669130886756</v>
+        <v>0.4454560940571964</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5137334953270173</v>
+        <v>0.5303019881341847</v>
       </c>
       <c r="M59" t="n">
-        <v>4.192052202289072</v>
+        <v>4.193144733448825</v>
       </c>
       <c r="N59" t="n">
-        <v>4.384757005062604</v>
+        <v>4.384951131560275</v>
       </c>
       <c r="O59" t="n">
-        <v>0.01158213208727017</v>
+        <v>0.01216147893062486</v>
       </c>
       <c r="P59" t="n">
-        <v>0.004501156376277752</v>
+        <v>0.004654816807526239</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.007971296892426216</v>
+        <v>0.007358421428858283</v>
       </c>
       <c r="R59" t="n">
-        <v>0.005960208500311382</v>
+        <v>0.006060300676625849</v>
       </c>
       <c r="S59" t="n">
-        <v>0.006862390422074775</v>
+        <v>0.006904487335112672</v>
       </c>
       <c r="T59" t="n">
-        <v>0.0200455496222555</v>
+        <v>0.02150230324014513</v>
       </c>
       <c r="U59" t="n">
-        <v>0.005691467311731722</v>
+        <v>0.005969074602656554</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01207448781874912</v>
+        <v>0.01080816827615231</v>
       </c>
       <c r="W59" t="n">
-        <v>0.005801047073611358</v>
+        <v>0.006041543118390611</v>
       </c>
       <c r="X59" t="n">
-        <v>0.006502913782881363</v>
+        <v>0.006590207800777785</v>
       </c>
     </row>
     <row r="60">
@@ -5211,61 +5211,61 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3195516907355711</v>
+        <v>0.2701213903358244</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2335821217569123</v>
+        <v>0.219369108257831</v>
       </c>
       <c r="M60" t="n">
-        <v>4.041987989944264</v>
+        <v>4.028615073796866</v>
       </c>
       <c r="N60" t="n">
-        <v>4.211515428719657</v>
+        <v>4.210327474966972</v>
       </c>
       <c r="O60" t="n">
-        <v>0.005119763135164285</v>
+        <v>0.008102504003424008</v>
       </c>
       <c r="P60" t="n">
-        <v>0.003631889696482466</v>
+        <v>0.003739665668404545</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.0009316206345992318</v>
+        <v>0.000859763141062474</v>
       </c>
       <c r="R60" t="n">
-        <v>0.001681791884465103</v>
+        <v>0.00150686814901146</v>
       </c>
       <c r="S60" t="n">
-        <v>0.004747628436562954</v>
+        <v>0.004414145453054481</v>
       </c>
       <c r="T60" t="n">
-        <v>0.008819318087748711</v>
+        <v>0.01614756307976096</v>
       </c>
       <c r="U60" t="n">
-        <v>0.005534195711211343</v>
+        <v>0.006333113862525901</v>
       </c>
       <c r="V60" t="n">
-        <v>0.00194546240985284</v>
+        <v>0.001853023033286949</v>
       </c>
       <c r="W60" t="n">
-        <v>0.002317269556391085</v>
+        <v>0.002245432903739793</v>
       </c>
       <c r="X60" t="n">
-        <v>0.005434801888720871</v>
+        <v>0.005140082501156945</v>
       </c>
     </row>
     <row r="61">
@@ -5291,61 +5291,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.3994271141921055</v>
+        <v>0.3824305879025255</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2756782749696744</v>
+        <v>0.3784415777697355</v>
       </c>
       <c r="M61" t="n">
-        <v>3.830195138216759</v>
+        <v>3.905635756552347</v>
       </c>
       <c r="N61" t="n">
-        <v>4.252954999705276</v>
+        <v>4.268540402248743</v>
       </c>
       <c r="O61" t="n">
-        <v>0.008322174340720792</v>
+        <v>0.009640839489208061</v>
       </c>
       <c r="P61" t="n">
-        <v>0.007467686495095413</v>
+        <v>0.006742247049603928</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.002297221168966474</v>
+        <v>0.002413070475309928</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01084892091240139</v>
+        <v>0.01137917106616181</v>
       </c>
       <c r="S61" t="n">
-        <v>0.04330034633966148</v>
+        <v>0.03426756185301367</v>
       </c>
       <c r="T61" t="n">
-        <v>0.01368291115118631</v>
+        <v>0.01813719565522166</v>
       </c>
       <c r="U61" t="n">
-        <v>0.009162469367370382</v>
+        <v>0.008043915473097317</v>
       </c>
       <c r="V61" t="n">
-        <v>0.0036607840956112</v>
+        <v>0.003789554067514406</v>
       </c>
       <c r="W61" t="n">
-        <v>0.009472411009186563</v>
+        <v>0.01071068628508081</v>
       </c>
       <c r="X61" t="n">
-        <v>0.299998870275473</v>
+        <v>0.1636596463908344</v>
       </c>
     </row>
     <row r="62">
@@ -5371,61 +5371,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.4202651317069659</v>
+        <v>0.3890643238636384</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2421632463898241</v>
+        <v>0.3564143887997979</v>
       </c>
       <c r="M62" t="n">
-        <v>4.183223779089313</v>
+        <v>4.193892861560939</v>
       </c>
       <c r="N62" t="n">
-        <v>4.200249399101945</v>
+        <v>4.238131510453202</v>
       </c>
       <c r="O62" t="n">
-        <v>0.01123108801070536</v>
+        <v>0.01232863395845482</v>
       </c>
       <c r="P62" t="n">
-        <v>0.005432178718210904</v>
+        <v>0.00482958285253626</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.00290047440866846</v>
+        <v>0.003051122715612231</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01810601368066709</v>
+        <v>0.0190032563904333</v>
       </c>
       <c r="S62" t="n">
-        <v>0.01193904718638896</v>
+        <v>0.01209216116779446</v>
       </c>
       <c r="T62" t="n">
-        <v>0.02259366616159376</v>
+        <v>0.0269073889567307</v>
       </c>
       <c r="U62" t="n">
-        <v>0.0107480665745413</v>
+        <v>0.007748336883180759</v>
       </c>
       <c r="V62" t="n">
-        <v>0.004557166406061409</v>
+        <v>0.004750919693635862</v>
       </c>
       <c r="W62" t="n">
-        <v>0.02498762865138897</v>
+        <v>0.02836492366237156</v>
       </c>
       <c r="X62" t="n">
-        <v>0.02284282963757141</v>
+        <v>0.02314181754324125</v>
       </c>
     </row>
     <row r="63">
@@ -5451,61 +5451,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4162364024212756</v>
+        <v>0.3916462498773384</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2947921559027571</v>
+        <v>0.3809708641257323</v>
       </c>
       <c r="M63" t="n">
-        <v>3.980573946132115</v>
+        <v>3.99353652419105</v>
       </c>
       <c r="N63" t="n">
-        <v>4.2526854592491</v>
+        <v>4.263370918780968</v>
       </c>
       <c r="O63" t="n">
-        <v>0.007618258486069474</v>
+        <v>0.008939155197760822</v>
       </c>
       <c r="P63" t="n">
-        <v>0.006235651905902674</v>
+        <v>0.005541419202863633</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.002233171301293958</v>
+        <v>0.002303082998971545</v>
       </c>
       <c r="R63" t="n">
-        <v>0.009131776200119221</v>
+        <v>0.009496093661040907</v>
       </c>
       <c r="S63" t="n">
-        <v>0.01904800218791809</v>
+        <v>0.01823943527992988</v>
       </c>
       <c r="T63" t="n">
-        <v>0.01253330145478524</v>
+        <v>0.01661789300024803</v>
       </c>
       <c r="U63" t="n">
-        <v>0.008194784136469738</v>
+        <v>0.006719099987909916</v>
       </c>
       <c r="V63" t="n">
-        <v>0.003445662796164592</v>
+        <v>0.003534367870453272</v>
       </c>
       <c r="W63" t="n">
-        <v>0.009269769219367971</v>
+        <v>0.0103381372460671</v>
       </c>
       <c r="X63" t="n">
-        <v>0.03832655172064543</v>
+        <v>0.03556224632722121</v>
       </c>
     </row>
     <row r="64">
@@ -5531,61 +5531,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.3674688031115195</v>
+        <v>0.3549664602965995</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2835993520358311</v>
+        <v>0.3887598197890027</v>
       </c>
       <c r="M64" t="n">
-        <v>3.69002349828743</v>
+        <v>3.849078802939207</v>
       </c>
       <c r="N64" t="n">
-        <v>4.24076839568089</v>
+        <v>4.267365956665933</v>
       </c>
       <c r="O64" t="n">
-        <v>0.009600420719320464</v>
+        <v>0.01032043546496979</v>
       </c>
       <c r="P64" t="n">
-        <v>0.006843091883926752</v>
+        <v>0.006258278086215151</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.003441943266742057</v>
+        <v>0.003604136512671363</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01853689026993374</v>
+        <v>0.01940042615569525</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0629493730322303</v>
+        <v>0.04690700657181941</v>
       </c>
       <c r="T64" t="n">
-        <v>0.0188845742419826</v>
+        <v>0.02197720594937932</v>
       </c>
       <c r="U64" t="n">
-        <v>0.009179766292756426</v>
+        <v>0.007587896249451093</v>
       </c>
       <c r="V64" t="n">
-        <v>0.005359724835456836</v>
+        <v>0.005628716070253269</v>
       </c>
       <c r="W64" t="n">
-        <v>0.02602387760784493</v>
+        <v>0.02927819615274029</v>
       </c>
       <c r="X64" t="n">
-        <v>1.298791284933649</v>
+        <v>0.5370578910792384</v>
       </c>
     </row>
     <row r="65">
@@ -5611,61 +5611,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4085515562507576</v>
+        <v>0.3852925812491872</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3572051596421338</v>
+        <v>0.4275026899754964</v>
       </c>
       <c r="M65" t="n">
-        <v>3.911842650195023</v>
+        <v>3.9329393834399</v>
       </c>
       <c r="N65" t="n">
-        <v>4.271918525482124</v>
+        <v>4.284788851865925</v>
       </c>
       <c r="O65" t="n">
-        <v>0.008189625107806501</v>
+        <v>0.009588041024421871</v>
       </c>
       <c r="P65" t="n">
-        <v>0.007857342428555257</v>
+        <v>0.00729169587264073</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.004118213947387659</v>
+        <v>0.004079253182098143</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01127484738795657</v>
+        <v>0.01174137839231607</v>
       </c>
       <c r="S65" t="n">
-        <v>0.03420275096795589</v>
+        <v>0.03258316845017842</v>
       </c>
       <c r="T65" t="n">
-        <v>0.01281255797332439</v>
+        <v>0.01726829213278973</v>
       </c>
       <c r="U65" t="n">
-        <v>0.009857591746217004</v>
+        <v>0.008863031469875495</v>
       </c>
       <c r="V65" t="n">
-        <v>0.006416571151373509</v>
+        <v>0.006432811249793004</v>
       </c>
       <c r="W65" t="n">
-        <v>0.01126503798897183</v>
+        <v>0.01260467285296109</v>
       </c>
       <c r="X65" t="n">
-        <v>0.1401142850923012</v>
+        <v>0.1231466442881697</v>
       </c>
     </row>
     <row r="66">
@@ -5691,61 +5691,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.396032261454521</v>
+        <v>0.3683063526754361</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2884765817511529</v>
+        <v>0.3888776883529966</v>
       </c>
       <c r="M66" t="n">
-        <v>3.957047851229053</v>
+        <v>3.984066840056817</v>
       </c>
       <c r="N66" t="n">
-        <v>4.242458771256108</v>
+        <v>4.267974551239664</v>
       </c>
       <c r="O66" t="n">
-        <v>0.009311986715177186</v>
+        <v>0.01022740431622302</v>
       </c>
       <c r="P66" t="n">
-        <v>0.007311112310467543</v>
+        <v>0.006636780705959949</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.003461088806570071</v>
+        <v>0.003567437122543475</v>
       </c>
       <c r="R66" t="n">
-        <v>0.0165300186540757</v>
+        <v>0.01710754705638919</v>
       </c>
       <c r="S66" t="n">
-        <v>0.03120241235925844</v>
+        <v>0.02972372273343506</v>
       </c>
       <c r="T66" t="n">
-        <v>0.01789754586177461</v>
+        <v>0.02156926153187303</v>
       </c>
       <c r="U66" t="n">
-        <v>0.009402402546946683</v>
+        <v>0.007850557177762682</v>
       </c>
       <c r="V66" t="n">
-        <v>0.005402558777041508</v>
+        <v>0.005615028199056855</v>
       </c>
       <c r="W66" t="n">
-        <v>0.02126695228410318</v>
+        <v>0.02363234198869242</v>
       </c>
       <c r="X66" t="n">
-        <v>0.1675654578265666</v>
+        <v>0.1466661052783577</v>
       </c>
     </row>
     <row r="67">
@@ -5771,61 +5771,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4199481453543742</v>
+        <v>0.3806197097218254</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3946078508399023</v>
+        <v>0.418032742536686</v>
       </c>
       <c r="M67" t="n">
-        <v>4.39633004726497</v>
+        <v>4.399192655214832</v>
       </c>
       <c r="N67" t="n">
-        <v>4.346590390295058</v>
+        <v>4.340914385485493</v>
       </c>
       <c r="O67" t="n">
-        <v>0.005686701770438183</v>
+        <v>0.007193971249980834</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01442873151916484</v>
+        <v>0.01425466572908437</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.004110207664754046</v>
+        <v>0.00452873974898259</v>
       </c>
       <c r="R67" t="n">
-        <v>0.009170189865629771</v>
+        <v>0.01016404578661367</v>
       </c>
       <c r="S67" t="n">
-        <v>0.05182825066811473</v>
+        <v>0.05807505928683451</v>
       </c>
       <c r="T67" t="n">
-        <v>0.008212848704652101</v>
+        <v>0.01079421400815452</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01324117789365526</v>
+        <v>0.01316740069119703</v>
       </c>
       <c r="V67" t="n">
-        <v>0.009267344104623071</v>
+        <v>0.01020210687249382</v>
       </c>
       <c r="W67" t="n">
-        <v>0.0130223229339061</v>
+        <v>0.0153594261159673</v>
       </c>
       <c r="X67" t="n">
-        <v>0.07949512915358359</v>
+        <v>0.08973189430895895</v>
       </c>
     </row>
     <row r="68">
@@ -5851,61 +5851,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4285024175374733</v>
+        <v>0.3886320832993509</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3887906156642397</v>
+        <v>0.4210306903076764</v>
       </c>
       <c r="M68" t="n">
-        <v>4.480409000587638</v>
+        <v>4.486141097122832</v>
       </c>
       <c r="N68" t="n">
-        <v>4.345648740316649</v>
+        <v>4.343721437452922</v>
       </c>
       <c r="O68" t="n">
-        <v>0.006211689159384393</v>
+        <v>0.007471739745642614</v>
       </c>
       <c r="P68" t="n">
-        <v>0.01721002036546732</v>
+        <v>0.016464983831219</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.004624504663032178</v>
+        <v>0.004768752034938825</v>
       </c>
       <c r="R68" t="n">
-        <v>0.01376600332741902</v>
+        <v>0.01462606207849732</v>
       </c>
       <c r="S68" t="n">
-        <v>0.01573549800616817</v>
+        <v>0.01676062048551463</v>
       </c>
       <c r="T68" t="n">
-        <v>0.01127892860952708</v>
+        <v>0.01445792251888601</v>
       </c>
       <c r="U68" t="n">
-        <v>0.01600385233372681</v>
+        <v>0.01494413338848269</v>
       </c>
       <c r="V68" t="n">
-        <v>0.008227197563280299</v>
+        <v>0.008441030529129987</v>
       </c>
       <c r="W68" t="n">
-        <v>0.01952518110900105</v>
+        <v>0.02218435845522141</v>
       </c>
       <c r="X68" t="n">
-        <v>0.02549850056088977</v>
+        <v>0.02709663194017002</v>
       </c>
     </row>
     <row r="69">
@@ -5931,61 +5931,61 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1574541057329026</v>
+        <v>0.1010562527983535</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2052525266463846</v>
+        <v>0.1728154412239898</v>
       </c>
       <c r="M69" t="n">
-        <v>4.332138796392004</v>
+        <v>4.331832199947486</v>
       </c>
       <c r="N69" t="n">
-        <v>4.301259047737942</v>
+        <v>4.292494753096341</v>
       </c>
       <c r="O69" t="n">
-        <v>0.008697335882864268</v>
+        <v>0.01227836227065161</v>
       </c>
       <c r="P69" t="n">
-        <v>0.005397398916447352</v>
+        <v>0.005171910872736205</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.003684531310681907</v>
+        <v>0.003621849674885609</v>
       </c>
       <c r="R69" t="n">
-        <v>0.004267353123611629</v>
+        <v>0.00393319929732327</v>
       </c>
       <c r="S69" t="n">
-        <v>0.004153910651498359</v>
+        <v>0.003959550028344942</v>
       </c>
       <c r="T69" t="n">
-        <v>0.01844820755406056</v>
+        <v>0.03119960710472874</v>
       </c>
       <c r="U69" t="n">
-        <v>0.009630476247740338</v>
+        <v>0.01126999654084391</v>
       </c>
       <c r="V69" t="n">
-        <v>0.005812052722773665</v>
+        <v>0.005660831473145589</v>
       </c>
       <c r="W69" t="n">
-        <v>0.005999333156887494</v>
+        <v>0.005770215295190083</v>
       </c>
       <c r="X69" t="n">
-        <v>0.006095744047079951</v>
+        <v>0.005911360709834601</v>
       </c>
     </row>
     <row r="70">
@@ -6011,61 +6011,61 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1548184556465437</v>
+        <v>0.09856641470047335</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2821165444330669</v>
+        <v>0.2505198071039456</v>
       </c>
       <c r="M70" t="n">
-        <v>4.393884558299479</v>
+        <v>4.407350183726711</v>
       </c>
       <c r="N70" t="n">
-        <v>4.356902676963256</v>
+        <v>4.347484747920573</v>
       </c>
       <c r="O70" t="n">
-        <v>0.007041754705486096</v>
+        <v>0.008900343123081009</v>
       </c>
       <c r="P70" t="n">
-        <v>0.009916987065314005</v>
+        <v>0.01082228342232973</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.005609818782489916</v>
+        <v>0.005510675920288217</v>
       </c>
       <c r="R70" t="n">
-        <v>0.004620176931972432</v>
+        <v>0.004298058762111358</v>
       </c>
       <c r="S70" t="n">
-        <v>0.006475976953657859</v>
+        <v>0.006106313610785698</v>
       </c>
       <c r="T70" t="n">
-        <v>0.01338069637391916</v>
+        <v>0.02032112834075771</v>
       </c>
       <c r="U70" t="n">
-        <v>0.01381308858031555</v>
+        <v>0.01783416247620849</v>
       </c>
       <c r="V70" t="n">
-        <v>0.009080225123130677</v>
+        <v>0.008790946560765173</v>
       </c>
       <c r="W70" t="n">
-        <v>0.006717288047944464</v>
+        <v>0.006477371296333982</v>
       </c>
       <c r="X70" t="n">
-        <v>0.009743408757198643</v>
+        <v>0.009295405813250108</v>
       </c>
     </row>
     <row r="71">
@@ -6091,61 +6091,61 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3259372934798359</v>
+        <v>0.269045723492097</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3495123073148794</v>
+        <v>0.3369175536426514</v>
       </c>
       <c r="M71" t="n">
-        <v>4.435983780461879</v>
+        <v>4.440211158709118</v>
       </c>
       <c r="N71" t="n">
-        <v>4.438765796292132</v>
+        <v>4.434015585986076</v>
       </c>
       <c r="O71" t="n">
-        <v>0.008538238534810201</v>
+        <v>0.009916293635171889</v>
       </c>
       <c r="P71" t="n">
-        <v>0.009237009000142833</v>
+        <v>0.008481972508508986</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.004661902567466843</v>
+        <v>0.00454921996702795</v>
       </c>
       <c r="R71" t="n">
-        <v>0.005153536413762512</v>
+        <v>0.004876232343190189</v>
       </c>
       <c r="S71" t="n">
-        <v>0.005562344271553641</v>
+        <v>0.005271864114310289</v>
       </c>
       <c r="T71" t="n">
-        <v>0.01387597470596059</v>
+        <v>0.01811938164306326</v>
       </c>
       <c r="U71" t="n">
-        <v>0.009902588064231206</v>
+        <v>0.009448036541916638</v>
       </c>
       <c r="V71" t="n">
-        <v>0.007437545349326493</v>
+        <v>0.00727444715017209</v>
       </c>
       <c r="W71" t="n">
-        <v>0.006776749424466729</v>
+        <v>0.006731810648263312</v>
       </c>
       <c r="X71" t="n">
-        <v>0.00693232532371009</v>
+        <v>0.006781796455711008</v>
       </c>
     </row>
     <row r="72">
@@ -6171,61 +6171,61 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3247916833722452</v>
+        <v>0.2663662166319356</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4127186230893385</v>
+        <v>0.391675815211094</v>
       </c>
       <c r="M72" t="n">
-        <v>4.528094939538367</v>
+        <v>4.543373877819946</v>
       </c>
       <c r="N72" t="n">
-        <v>4.500728602013576</v>
+        <v>4.497098791971776</v>
       </c>
       <c r="O72" t="n">
-        <v>0.006160620005598041</v>
+        <v>0.006617664925347296</v>
       </c>
       <c r="P72" t="n">
-        <v>0.007061793149966656</v>
+        <v>0.006726549259816711</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.005623081508063347</v>
+        <v>0.005441161779033739</v>
       </c>
       <c r="R72" t="n">
-        <v>0.004398654641003785</v>
+        <v>0.004159600483390923</v>
       </c>
       <c r="S72" t="n">
-        <v>0.006047072051250384</v>
+        <v>0.005724517079152029</v>
       </c>
       <c r="T72" t="n">
-        <v>0.008992879365170294</v>
+        <v>0.01033473285357992</v>
       </c>
       <c r="U72" t="n">
-        <v>0.008021590002114092</v>
+        <v>0.007885581611308916</v>
       </c>
       <c r="V72" t="n">
-        <v>0.009016568120366681</v>
+        <v>0.008797125155105638</v>
       </c>
       <c r="W72" t="n">
-        <v>0.006169601223022439</v>
+        <v>0.00603326875278102</v>
       </c>
       <c r="X72" t="n">
-        <v>0.007714964968362422</v>
+        <v>0.00755224364971</v>
       </c>
     </row>
     <row r="73">
@@ -6251,61 +6251,61 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.08004889403840529</v>
+        <v>0.04025276581779436</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08113991389542105</v>
+        <v>0.05536347232051227</v>
       </c>
       <c r="M73" t="n">
-        <v>4.341167164957967</v>
+        <v>4.33317781811658</v>
       </c>
       <c r="N73" t="n">
-        <v>4.328594414246572</v>
+        <v>4.324606523263236</v>
       </c>
       <c r="O73" t="n">
-        <v>0.01323244292225256</v>
+        <v>0.02659825137779304</v>
       </c>
       <c r="P73" t="n">
-        <v>0.01256801918834716</v>
+        <v>0.01762178476435033</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.001841608910406477</v>
+        <v>0.001801163706178717</v>
       </c>
       <c r="R73" t="n">
-        <v>0.002548885856111626</v>
+        <v>0.002341007847490206</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003786034117191857</v>
+        <v>0.0002709741151206127</v>
       </c>
       <c r="T73" t="n">
-        <v>0.03777100137267746</v>
+        <v>0.08962191717353805</v>
       </c>
       <c r="U73" t="n">
-        <v>0.0252108259623172</v>
+        <v>0.04965652585052124</v>
       </c>
       <c r="V73" t="n">
-        <v>0.003453255620810314</v>
+        <v>0.003357113370447076</v>
       </c>
       <c r="W73" t="n">
-        <v>0.004161393983429871</v>
+        <v>0.004033240478339807</v>
       </c>
       <c r="X73" t="n">
-        <v>0.003226953352581988</v>
+        <v>0.003165349293642675</v>
       </c>
     </row>
     <row r="74">
@@ -6331,61 +6331,61 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08447253447494207</v>
+        <v>0.04324396783538792</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1625880973863177</v>
+        <v>0.1245818164796632</v>
       </c>
       <c r="M74" t="n">
-        <v>4.398896285344729</v>
+        <v>4.406169716270606</v>
       </c>
       <c r="N74" t="n">
-        <v>4.385985377291092</v>
+        <v>4.378743327034374</v>
       </c>
       <c r="O74" t="n">
-        <v>0.006292807511356764</v>
+        <v>0.009299116610108366</v>
       </c>
       <c r="P74" t="n">
-        <v>0.008619415554112586</v>
+        <v>0.009721798133352057</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.003381667397581816</v>
+        <v>0.003345567622821832</v>
       </c>
       <c r="R74" t="n">
-        <v>0.002113418898904021</v>
+        <v>0.001964023638997771</v>
       </c>
       <c r="S74" t="n">
-        <v>0.003726249519892874</v>
+        <v>0.003551114974871843</v>
       </c>
       <c r="T74" t="n">
-        <v>0.01629588272303076</v>
+        <v>0.02882909613908331</v>
       </c>
       <c r="U74" t="n">
-        <v>0.01450349593892756</v>
+        <v>0.02141376961574822</v>
       </c>
       <c r="V74" t="n">
-        <v>0.005347455124597961</v>
+        <v>0.005249601129374704</v>
       </c>
       <c r="W74" t="n">
-        <v>0.003684017043327827</v>
+        <v>0.003569502231910481</v>
       </c>
       <c r="X74" t="n">
-        <v>0.00562392175559857</v>
+        <v>0.005457597058072861</v>
       </c>
     </row>
     <row r="75">
@@ -6411,61 +6411,61 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2074205046880389</v>
+        <v>0.148541542472987</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2623727640782005</v>
+        <v>0.236417971840428</v>
       </c>
       <c r="M75" t="n">
-        <v>4.197065933067138</v>
+        <v>4.193647807726889</v>
       </c>
       <c r="N75" t="n">
-        <v>4.282963131348233</v>
+        <v>4.271708687129742</v>
       </c>
       <c r="O75" t="n">
-        <v>0.006245120541096643</v>
+        <v>0.008065936287791063</v>
       </c>
       <c r="P75" t="n">
-        <v>0.009670164516327455</v>
+        <v>0.01016981659294952</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.004021698121183217</v>
+        <v>0.00393681174460205</v>
       </c>
       <c r="R75" t="n">
-        <v>0.004762930561152022</v>
+        <v>0.004476456084793635</v>
       </c>
       <c r="S75" t="n">
-        <v>0.00717411220561622</v>
+        <v>0.006950310909617806</v>
       </c>
       <c r="T75" t="n">
-        <v>0.01211322190424821</v>
+        <v>0.0181352741380212</v>
       </c>
       <c r="U75" t="n">
-        <v>0.01264484894402839</v>
+        <v>0.01515749254809914</v>
       </c>
       <c r="V75" t="n">
-        <v>0.006370435967034196</v>
+        <v>0.006179064498296491</v>
       </c>
       <c r="W75" t="n">
-        <v>0.006517516058862821</v>
+        <v>0.006389101105130059</v>
       </c>
       <c r="X75" t="n">
-        <v>0.01087003527579221</v>
+        <v>0.01062884933147779</v>
       </c>
     </row>
     <row r="76">
@@ -6491,61 +6491,61 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02053193249929068</v>
+        <v>0.006369374384653942</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02514680554462075</v>
+        <v>0.01262781321212834</v>
       </c>
       <c r="M76" t="n">
-        <v>4.359073637778749</v>
+        <v>4.367107331905855</v>
       </c>
       <c r="N76" t="n">
-        <v>4.318116573623967</v>
+        <v>4.315760703282015</v>
       </c>
       <c r="O76" t="n">
-        <v>0.04210713408437999</v>
+        <v>0.1218390082049329</v>
       </c>
       <c r="P76" t="n">
-        <v>0.02727962166551377</v>
+        <v>0.06968555321840707</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.002067085808971351</v>
+        <v>0.002082840375186057</v>
       </c>
       <c r="R76" t="n">
-        <v>0.002217603118285098</v>
+        <v>0.002115922491412743</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0007945353108686339</v>
+        <v>0.000760590827031153</v>
       </c>
       <c r="T76" t="n">
-        <v>0.1416058013619185</v>
+        <v>0.4990920112109982</v>
       </c>
       <c r="U76" t="n">
-        <v>0.08361898104463897</v>
+        <v>0.2838784788610343</v>
       </c>
       <c r="V76" t="n">
-        <v>0.003583708870962505</v>
+        <v>0.003522375690179734</v>
       </c>
       <c r="W76" t="n">
-        <v>0.003737440602601527</v>
+        <v>0.003680214891991365</v>
       </c>
       <c r="X76" t="n">
-        <v>0.002698813025432731</v>
+        <v>0.002684770985858464</v>
       </c>
     </row>
     <row r="77">
@@ -6571,61 +6571,61 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03782537579660925</v>
+        <v>0.014699157934358</v>
       </c>
       <c r="L77" t="n">
-        <v>0.08097815804016646</v>
+        <v>0.04735676941388613</v>
       </c>
       <c r="M77" t="n">
-        <v>4.268656568147811</v>
+        <v>4.273959898801073</v>
       </c>
       <c r="N77" t="n">
-        <v>4.245138155328809</v>
+        <v>4.239646620283942</v>
       </c>
       <c r="O77" t="n">
-        <v>0.01381894615408611</v>
+        <v>0.0282764774980253</v>
       </c>
       <c r="P77" t="n">
-        <v>0.003757490358159672</v>
+        <v>0.003658808990467539</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.002032619045363282</v>
+        <v>0.001960529131459165</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0003791909046618231</v>
+        <v>0.0003432916313894685</v>
       </c>
       <c r="S77" t="n">
-        <v>0.001767978679563574</v>
+        <v>0.001684945351145738</v>
       </c>
       <c r="T77" t="n">
-        <v>0.03403154285305804</v>
+        <v>0.08653092553925498</v>
       </c>
       <c r="U77" t="n">
-        <v>0.01318563316280446</v>
+        <v>0.02143622921036587</v>
       </c>
       <c r="V77" t="n">
-        <v>0.003054291550795958</v>
+        <v>0.002944521394992629</v>
       </c>
       <c r="W77" t="n">
-        <v>0.002024625475944558</v>
+        <v>0.001997982272809138</v>
       </c>
       <c r="X77" t="n">
-        <v>0.00276789467274687</v>
+        <v>0.002713175557885006</v>
       </c>
     </row>
     <row r="78">
@@ -6651,61 +6651,61 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02723295651487582</v>
+        <v>0.009272849175076056</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0766008676009966</v>
+        <v>0.04495372864170763</v>
       </c>
       <c r="M78" t="n">
-        <v>4.413573948301897</v>
+        <v>4.409715680264562</v>
       </c>
       <c r="N78" t="n">
-        <v>4.37829161508492</v>
+        <v>4.36338413632331</v>
       </c>
       <c r="O78" t="n">
-        <v>0.006302566309750019</v>
+        <v>0.01123710931967161</v>
       </c>
       <c r="P78" t="n">
-        <v>1.000000000071305e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.001805496917605349</v>
+        <v>0.001851853697068877</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0001674553222235624</v>
+        <v>0.000128136724843387</v>
       </c>
       <c r="S78" t="n">
-        <v>1.000000000000033e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="T78" t="n">
-        <v>0.0215391969134919</v>
+        <v>0.04629003468484238</v>
       </c>
       <c r="U78" t="n">
-        <v>0.0189688646835046</v>
+        <v>0.02275019418894108</v>
       </c>
       <c r="V78" t="n">
-        <v>0.002891265875586965</v>
+        <v>0.002932172079670464</v>
       </c>
       <c r="W78" t="n">
-        <v>0.00170555842652797</v>
+        <v>0.001672825453689347</v>
       </c>
       <c r="X78" t="n">
-        <v>0.002934388439255799</v>
+        <v>0.003015327846111883</v>
       </c>
     </row>
     <row r="79">
@@ -6725,67 +6725,67 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2905655997701949</v>
+        <v>0.2305198222631793</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3193251383257389</v>
+        <v>0.2944840336380979</v>
       </c>
       <c r="M79" t="n">
-        <v>4.384688376048642</v>
+        <v>4.376078257807563</v>
       </c>
       <c r="N79" t="n">
-        <v>4.414745075458724</v>
+        <v>4.374736024285611</v>
       </c>
       <c r="O79" t="n">
-        <v>0.003147207099280328</v>
+        <v>0.003854199158449958</v>
       </c>
       <c r="P79" t="n">
-        <v>0.00181777187931982</v>
+        <v>0.001653553899850292</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.001444320371422225</v>
+        <v>0.00139301954204593</v>
       </c>
       <c r="R79" t="n">
-        <v>0.001630442173610273</v>
+        <v>0.00149653264250928</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0005977485697859727</v>
+        <v>0.4999999999998958</v>
       </c>
       <c r="T79" t="n">
-        <v>0.00607770090173849</v>
+        <v>0.00915740153640349</v>
       </c>
       <c r="U79" t="n">
-        <v>0.002150034004461958</v>
+        <v>0.002292255310038759</v>
       </c>
       <c r="V79" t="n">
-        <v>0.002565919663114426</v>
+        <v>0.002429698101568048</v>
       </c>
       <c r="W79" t="n">
-        <v>0.002597945957028094</v>
+        <v>0.002361342428098995</v>
       </c>
       <c r="X79" t="n">
-        <v>0.154595460590586</v>
+        <v>11203.1950119143</v>
       </c>
     </row>
     <row r="80">
@@ -6805,67 +6805,67 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1624757209231998</v>
+        <v>0.1040560020796793</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2462244769929051</v>
+        <v>0.218476711672129</v>
       </c>
       <c r="M80" t="n">
-        <v>4.522041228329741</v>
+        <v>4.534282997629987</v>
       </c>
       <c r="N80" t="n">
-        <v>4.466768919963216</v>
+        <v>4.420265770976781</v>
       </c>
       <c r="O80" t="n">
-        <v>0.004352998420737021</v>
+        <v>0.005932839983048368</v>
       </c>
       <c r="P80" t="n">
-        <v>0.002638442960042925</v>
+        <v>0.002691147644599539</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.001807076613868658</v>
+        <v>0.001773653128436966</v>
       </c>
       <c r="R80" t="n">
-        <v>0.001726803461836381</v>
+        <v>0.001594195191514418</v>
       </c>
       <c r="S80" t="n">
-        <v>1.000000001324653e-05</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="T80" t="n">
-        <v>0.01046157986673176</v>
+        <v>0.0176857938648153</v>
       </c>
       <c r="U80" t="n">
-        <v>0.003125894024472116</v>
+        <v>0.00431281231305578</v>
       </c>
       <c r="V80" t="n">
-        <v>0.003152564688256193</v>
+        <v>0.003063732084893318</v>
       </c>
       <c r="W80" t="n">
-        <v>0.002868581738658547</v>
+        <v>0.002588934858855894</v>
       </c>
       <c r="X80" t="n">
-        <v>0.1347039345787046</v>
+        <v>13589.83477000429</v>
       </c>
     </row>
     <row r="81">
@@ -6885,67 +6885,67 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2809117196549366</v>
+        <v>0.2167356659231921</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2568426903990036</v>
+        <v>0.2375152663776194</v>
       </c>
       <c r="M81" t="n">
-        <v>4.54352300571286</v>
+        <v>4.524759469348124</v>
       </c>
       <c r="N81" t="n">
-        <v>4.588713187220218</v>
+        <v>4.590472602523563</v>
       </c>
       <c r="O81" t="n">
-        <v>0.003861132810210435</v>
+        <v>0.005221804972666136</v>
       </c>
       <c r="P81" t="n">
-        <v>0.002252332360339448</v>
+        <v>0.001997056594067571</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.001123934038745844</v>
+        <v>0.001088732580032211</v>
       </c>
       <c r="R81" t="n">
-        <v>0.001628818677767283</v>
+        <v>0.00154910644240964</v>
       </c>
       <c r="S81" t="n">
-        <v>1.000000000000264e-05</v>
+        <v>1.000000000000354e-05</v>
       </c>
       <c r="T81" t="n">
-        <v>0.007836402550389192</v>
+        <v>0.01258661710934789</v>
       </c>
       <c r="U81" t="n">
-        <v>0.003260238794465878</v>
+        <v>0.004384053553348552</v>
       </c>
       <c r="V81" t="n">
-        <v>0.001997245048029446</v>
+        <v>0.001884332641096902</v>
       </c>
       <c r="W81" t="n">
-        <v>0.002508354863096412</v>
+        <v>0.002321714442568805</v>
       </c>
       <c r="X81" t="n">
-        <v>0.1140826876458235</v>
+        <v>0.1523363299204039</v>
       </c>
     </row>
     <row r="82">
@@ -6965,67 +6965,67 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2356503211145312</v>
+        <v>0.1711357406879873</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1477343920944866</v>
+        <v>0.1579524816041986</v>
       </c>
       <c r="M82" t="n">
-        <v>4.465692697328193</v>
+        <v>4.428864509341516</v>
       </c>
       <c r="N82" t="n">
-        <v>4.595725775023816</v>
+        <v>4.608545421920391</v>
       </c>
       <c r="O82" t="n">
-        <v>0.006899496387278038</v>
+        <v>0.01092006375039811</v>
       </c>
       <c r="P82" t="n">
-        <v>0.003194739030479679</v>
+        <v>0.003044122767252801</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.000957498804501874</v>
+        <v>0.000956867272956782</v>
       </c>
       <c r="R82" t="n">
-        <v>0.001793513933249582</v>
+        <v>0.001766495268380672</v>
       </c>
       <c r="S82" t="n">
-        <v>0.2652770548310455</v>
+        <v>0.001008768334441586</v>
       </c>
       <c r="T82" t="n">
-        <v>0.01936406559155384</v>
+        <v>0.0329163267552593</v>
       </c>
       <c r="U82" t="n">
-        <v>0.01028287567607717</v>
+        <v>0.008802982640478074</v>
       </c>
       <c r="V82" t="n">
-        <v>0.001674904082703602</v>
+        <v>0.00165411260275891</v>
       </c>
       <c r="W82" t="n">
-        <v>0.00273975646150765</v>
+        <v>0.002798957264991211</v>
       </c>
       <c r="X82" t="n">
-        <v>3200.868471068145</v>
+        <v>0.4388296865109163</v>
       </c>
     </row>
     <row r="83">
@@ -7045,65 +7045,65 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1900383461359677</v>
+        <v>0.1274211052633809</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1855790480569224</v>
+        <v>0.1595764234582905</v>
       </c>
       <c r="M83" t="n">
-        <v>4.580927191812872</v>
+        <v>4.571265893551568</v>
       </c>
       <c r="N83" t="n">
-        <v>4.571329756778653</v>
+        <v>4.569304386046905</v>
       </c>
       <c r="O83" t="n">
-        <v>0.004106819793420861</v>
+        <v>0.006094554952550324</v>
       </c>
       <c r="P83" t="n">
-        <v>0.001704682090402879</v>
+        <v>0.001730887138065959</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.000998696866006887</v>
+        <v>0.0009835348495635832</v>
       </c>
       <c r="R83" t="n">
-        <v>0.00142244321359066</v>
+        <v>0.001338599811037459</v>
       </c>
       <c r="S83" t="n">
-        <v>1.000000000025039e-05</v>
+        <v>1.000000000002187e-05</v>
       </c>
       <c r="T83" t="n">
-        <v>0.009656310806411373</v>
+        <v>0.01729650461460607</v>
       </c>
       <c r="U83" t="n">
-        <v>0.004878179448193665</v>
+        <v>0.006581918783929049</v>
       </c>
       <c r="V83" t="n">
-        <v>0.001816976652035546</v>
+        <v>0.001738103584508633</v>
       </c>
       <c r="W83" t="n">
-        <v>0.002365581625461602</v>
+        <v>0.002098805333429218</v>
       </c>
       <c r="X83" t="n">
-        <v>0.130510815641632</v>
+        <v>0.165869421217256</v>
       </c>
     </row>
     <row r="84">
@@ -7123,65 +7123,65 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1700871734410854</v>
+        <v>0.1109470721818669</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2305510722140747</v>
+        <v>0.2282017934601235</v>
       </c>
       <c r="M84" t="n">
-        <v>4.554043371413063</v>
+        <v>4.586544133145753</v>
       </c>
       <c r="N84" t="n">
-        <v>4.502375865319721</v>
+        <v>4.493902833405971</v>
       </c>
       <c r="O84" t="n">
-        <v>0.004580612431084036</v>
+        <v>0.005357604577401585</v>
       </c>
       <c r="P84" t="n">
-        <v>1.000000000001186e-05</v>
+        <v>1.000000000000032e-05</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.001674498145792546</v>
+        <v>0.001972072971827946</v>
       </c>
       <c r="R84" t="n">
-        <v>0.002005585337766274</v>
+        <v>0.001931401485914033</v>
       </c>
       <c r="S84" t="n">
-        <v>1.000000000000519e-05</v>
+        <v>1.000000000000071e-05</v>
       </c>
       <c r="T84" t="n">
-        <v>0.0116420548043375</v>
+        <v>0.01667233056936858</v>
       </c>
       <c r="U84" t="n">
-        <v>0.006982834285418339</v>
+        <v>0.005083044261782481</v>
       </c>
       <c r="V84" t="n">
-        <v>0.002968594967667026</v>
+        <v>0.00361904771543812</v>
       </c>
       <c r="W84" t="n">
-        <v>0.003366699868374119</v>
+        <v>0.003196803436588013</v>
       </c>
       <c r="X84" t="n">
-        <v>0.1163796120549553</v>
+        <v>0.1401906687136986</v>
       </c>
     </row>
     <row r="85">
@@ -7201,65 +7201,67 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.234087371719241</v>
+        <v>0.2332956893959356</v>
       </c>
       <c r="L85" t="n">
-        <v>0.280140121329051</v>
+        <v>0.2566636548534066</v>
       </c>
       <c r="M85" t="n">
-        <v>4.488615918273156</v>
+        <v>4.323756426548535</v>
       </c>
       <c r="N85" t="n">
-        <v>4.486629258925698</v>
+        <v>4.387827633730484</v>
       </c>
       <c r="O85" t="n">
-        <v>0.003296136043681622</v>
+        <v>0.004609996991013587</v>
       </c>
       <c r="P85" t="n">
-        <v>1.000000000000389e-05</v>
+        <v>0.001674315511436737</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.001469872716214687</v>
+        <v>0.001092119088020634</v>
       </c>
       <c r="R85" t="n">
-        <v>0.001743971564358019</v>
+        <v>0.001439813448878605</v>
       </c>
       <c r="S85" t="n">
-        <v>1.000000000000016e-05</v>
+        <v>0.4999999999881212</v>
       </c>
       <c r="T85" t="n">
-        <v>0.007173279975091383</v>
+        <v>0.01180025961016239</v>
       </c>
       <c r="U85" t="n">
-        <v>0.008869431645645152</v>
+        <v>0.003337103167988728</v>
       </c>
       <c r="V85" t="n">
-        <v>0.002771769748580426</v>
+        <v>0.00191774101406797</v>
       </c>
       <c r="W85" t="n">
-        <v>0.00281278493756876</v>
+        <v>0.002198307044018838</v>
       </c>
       <c r="X85" t="n">
-        <v>0.1248270624367359</v>
+        <v>17798.44572577703</v>
       </c>
     </row>
     <row r="86">
@@ -7279,65 +7281,67 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1246919775437176</v>
+        <v>0.1064698714707798</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1550425121143549</v>
+        <v>0.1909897613905012</v>
       </c>
       <c r="M86" t="n">
-        <v>4.567691173450373</v>
+        <v>4.52106968442537</v>
       </c>
       <c r="N86" t="n">
-        <v>4.512548632694066</v>
+        <v>4.434172483894417</v>
       </c>
       <c r="O86" t="n">
-        <v>0.005849095074375368</v>
+        <v>0.006626556546612984</v>
       </c>
       <c r="P86" t="n">
-        <v>1.000000000000081e-05</v>
+        <v>0.0026970589683277</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.001430381346093342</v>
+        <v>0.001543818943479143</v>
       </c>
       <c r="R86" t="n">
-        <v>0.001787067398720183</v>
+        <v>0.001605790934941762</v>
       </c>
       <c r="S86" t="n">
-        <v>1.000000000000013e-05</v>
+        <v>0.4999999999722498</v>
       </c>
       <c r="T86" t="n">
-        <v>0.01733173470967076</v>
+        <v>0.02036376328717037</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01091931350920984</v>
+        <v>0.006088301096343186</v>
       </c>
       <c r="V86" t="n">
-        <v>0.002402706329626853</v>
+        <v>0.002602085290834123</v>
       </c>
       <c r="W86" t="n">
-        <v>0.002984945666529529</v>
+        <v>0.002639614053432804</v>
       </c>
       <c r="X86" t="n">
-        <v>0.1683221126162023</v>
+        <v>21105.47992074858</v>
       </c>
     </row>
     <row r="87">
@@ -7357,65 +7361,67 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1836947289226107</v>
+        <v>0.1614792491899684</v>
       </c>
       <c r="L87" t="n">
-        <v>0.2687473467167814</v>
+        <v>0.149436581711943</v>
       </c>
       <c r="M87" t="n">
-        <v>4.672696706020264</v>
+        <v>4.414995507077074</v>
       </c>
       <c r="N87" t="n">
-        <v>4.616044454976699</v>
+        <v>4.607123237798318</v>
       </c>
       <c r="O87" t="n">
-        <v>0.004964626442924765</v>
+        <v>0.0134227901578177</v>
       </c>
       <c r="P87" t="n">
-        <v>1e-05</v>
+        <v>0.004106578591703474</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.002033793100026232</v>
+        <v>0.001078696378649758</v>
       </c>
       <c r="R87" t="n">
-        <v>0.002179271288262475</v>
+        <v>0.00195768345765481</v>
       </c>
       <c r="S87" t="n">
-        <v>1e-05</v>
+        <v>0.001064016368776699</v>
       </c>
       <c r="T87" t="n">
-        <v>0.01278513210747983</v>
+        <v>0.04350748489075525</v>
       </c>
       <c r="U87" t="n">
-        <v>0.01022632915901991</v>
+        <v>0.01124698748966091</v>
       </c>
       <c r="V87" t="n">
-        <v>0.003740007043998683</v>
+        <v>0.001794678405178917</v>
       </c>
       <c r="W87" t="n">
-        <v>0.003549729974510247</v>
+        <v>0.003156788775951199</v>
       </c>
       <c r="X87" t="n">
-        <v>0.1202396730359505</v>
+        <v>0.4591375478199</v>
       </c>
     </row>
     <row r="88">
@@ -7435,65 +7441,67 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2272428571521708</v>
+        <v>0.2251944037531621</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1649949629160864</v>
+        <v>0.2467197247478871</v>
       </c>
       <c r="M88" t="n">
-        <v>4.514091802725877</v>
+        <v>4.527491454904385</v>
       </c>
       <c r="N88" t="n">
-        <v>4.617609265408083</v>
+        <v>4.594038383802556</v>
       </c>
       <c r="O88" t="n">
-        <v>0.005274106878235054</v>
+        <v>0.005499781291058146</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0005387753711153764</v>
+        <v>0.002302711578835167</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.0008534370449575995</v>
+        <v>0.00117515319418045</v>
       </c>
       <c r="R88" t="n">
-        <v>0.00139590313937179</v>
+        <v>0.00170909387163899</v>
       </c>
       <c r="S88" t="n">
-        <v>0.02094995847834549</v>
+        <v>1.000000055999975e-05</v>
       </c>
       <c r="T88" t="n">
-        <v>0.0003922760583934117</v>
+        <v>0.0134474628059033</v>
       </c>
       <c r="U88" t="n">
-        <v>0.02552561138224623</v>
+        <v>0.004550015910909853</v>
       </c>
       <c r="V88" t="n">
-        <v>0.001462338392792775</v>
+        <v>0.002010131728763318</v>
       </c>
       <c r="W88" t="n">
-        <v>0.002501113444407036</v>
+        <v>0.002550482446634304</v>
       </c>
       <c r="X88" t="n">
-        <v>35.15663364933559</v>
+        <v>0.1379460112251513</v>
       </c>
     </row>
     <row r="89">
@@ -7513,65 +7521,65 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3475847711320364</v>
+        <v>0.2890984163093071</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3217435357824465</v>
+        <v>0.2886608425446121</v>
       </c>
       <c r="M89" t="n">
-        <v>4.486632846602943</v>
+        <v>4.444533319955882</v>
       </c>
       <c r="N89" t="n">
-        <v>4.608999946874406</v>
+        <v>4.575225185037346</v>
       </c>
       <c r="O89" t="n">
-        <v>0.004325496204075163</v>
+        <v>0.005662441906687249</v>
       </c>
       <c r="P89" t="n">
-        <v>0.001457355749193634</v>
+        <v>0.0004589797455528473</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.001405183441218782</v>
+        <v>0.001354743626940914</v>
       </c>
       <c r="R89" t="n">
-        <v>0.001920231400108025</v>
+        <v>0.001814219297549352</v>
       </c>
       <c r="S89" t="n">
-        <v>1.000000000000103e-05</v>
+        <v>0.4999999999999998</v>
       </c>
       <c r="T89" t="n">
-        <v>0.008759831028461416</v>
+        <v>0.01481962175671863</v>
       </c>
       <c r="U89" t="n">
-        <v>0.004370777636010657</v>
+        <v>0.003424862023049758</v>
       </c>
       <c r="V89" t="n">
-        <v>0.00242289800528199</v>
+        <v>0.002337540314800184</v>
       </c>
       <c r="W89" t="n">
-        <v>0.002867491650848291</v>
+        <v>0.00265485197887359</v>
       </c>
       <c r="X89" t="n">
-        <v>0.07638662622600033</v>
+        <v>12480.96493714601</v>
       </c>
     </row>
     <row r="90">
@@ -7593,63 +7601,65 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.559419327333303</v>
+        <v>0.5773718555675572</v>
       </c>
       <c r="L90" t="n">
-        <v>0.5226646055343052</v>
+        <v>0.5405373652448993</v>
       </c>
       <c r="M90" t="n">
-        <v>4.527214580177771</v>
+        <v>4.57712737558739</v>
       </c>
       <c r="N90" t="n">
-        <v>4.270833915358878</v>
+        <v>4.29468813421159</v>
       </c>
       <c r="O90" t="n">
-        <v>0.004522063673720365</v>
+        <v>0.003793110711479149</v>
       </c>
       <c r="P90" t="n">
-        <v>0.003737985628427708</v>
+        <v>0.004554100338876091</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.00814934061222752</v>
+        <v>0.00721329704414119</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01269008219835107</v>
+        <v>0.01222860324070413</v>
       </c>
       <c r="S90" t="n">
-        <v>0.002328855460780322</v>
+        <v>0.002106833036796152</v>
       </c>
       <c r="T90" t="n">
-        <v>0.009412906414151288</v>
+        <v>0.006412512454879245</v>
       </c>
       <c r="U90" t="n">
-        <v>0.006060780849739942</v>
+        <v>0.005672224797343496</v>
       </c>
       <c r="V90" t="n">
-        <v>0.01360972086847957</v>
+        <v>0.006348622045225643</v>
       </c>
       <c r="W90" t="n">
-        <v>0.0327775848483394</v>
+        <v>0.03082208696147654</v>
       </c>
       <c r="X90" t="n">
-        <v>0.06528677640611645</v>
+        <v>0.05673243407800624</v>
       </c>
     </row>
   </sheetData>
